--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" state="visible" r:id="rId1"/>
@@ -2413,8 +2413,8 @@
     <col width="25.5" bestFit="1" customWidth="1" style="23" min="7" max="7"/>
     <col width="31.75" bestFit="1" customWidth="1" style="23" min="8" max="8"/>
     <col width="33.875" bestFit="1" customWidth="1" style="23" min="9" max="9"/>
-    <col width="9.125" customWidth="1" style="23" min="10" max="80"/>
-    <col width="9.125" customWidth="1" style="23" min="81" max="16384"/>
+    <col width="9.125" customWidth="1" style="23" min="10" max="81"/>
+    <col width="9.125" customWidth="1" style="23" min="82" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.4" customHeight="1">
@@ -5815,8 +5815,8 @@
     <col width="8.375" bestFit="1" customWidth="1" style="46" min="16" max="18"/>
     <col width="10.75" customWidth="1" style="46" min="19" max="19"/>
     <col width="10" bestFit="1" customWidth="1" style="46" min="20" max="20"/>
-    <col width="9" customWidth="1" style="47" min="21" max="30"/>
-    <col width="9" customWidth="1" style="47" min="31" max="16384"/>
+    <col width="9" customWidth="1" style="47" min="21" max="31"/>
+    <col width="9" customWidth="1" style="47" min="32" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customFormat="1" customHeight="1" s="46">
@@ -8887,8 +8887,8 @@
     <col width="48" customWidth="1" style="10" min="9" max="9"/>
     <col width="150.5" customWidth="1" style="64" min="10" max="10"/>
     <col width="8.875" customWidth="1" style="66" min="11" max="11"/>
-    <col width="8.875" customWidth="1" style="36" min="12" max="54"/>
-    <col width="8.875" customWidth="1" style="36" min="55" max="16384"/>
+    <col width="8.875" customWidth="1" style="36" min="12" max="55"/>
+    <col width="8.875" customWidth="1" style="36" min="56" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28032,8 +28032,8 @@
     <col width="5.125" customWidth="1" style="35" min="27" max="27"/>
     <col width="5" customWidth="1" style="35" min="28" max="28"/>
     <col width="5.25" customWidth="1" style="35" min="29" max="29"/>
-    <col width="9" customWidth="1" style="9" min="30" max="128"/>
-    <col width="9" customWidth="1" style="9" min="129" max="16384"/>
+    <col width="9" customWidth="1" style="9" min="30" max="129"/>
+    <col width="9" customWidth="1" style="9" min="130" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -28265,10 +28265,10 @@
         <v>1.3</v>
       </c>
       <c r="D8" s="32" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E8" s="32" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -28284,7 +28284,7 @@
         <v>1.5</v>
       </c>
       <c r="E9" s="32" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -28300,7 +28300,7 @@
         <v>0.7</v>
       </c>
       <c r="E10" s="32" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -28310,13 +28310,13 @@
         </is>
       </c>
       <c r="B11" s="32" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="D11" s="32" t="n">
         <v>0.7</v>
       </c>
       <c r="E11" s="32" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -10312,7 +10312,11 @@
           <t>万历二十一年李东璧病逝，终年76岁…</t>
         </is>
       </c>
-      <c r="K35" s="50" t="inlineStr"/>
+      <c r="K35" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Music/Story/寻幽探胜.mp3</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="50" t="inlineStr">
@@ -19700,7 +19704,7 @@
       </c>
       <c r="K273" s="51" t="inlineStr">
         <is>
-          <t>res://Assets/Music/020/圍剿夜襲.mp3</t>
+          <t>res://Assets/Music/Story/020/圍剿夜襲.mp3</t>
         </is>
       </c>
     </row>

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="3" activeTab="9" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" state="visible" r:id="rId1"/>
@@ -2417,8 +2417,8 @@
     <col width="25.5" bestFit="1" customWidth="1" style="23" min="7" max="7"/>
     <col width="31.75" bestFit="1" customWidth="1" style="23" min="8" max="8"/>
     <col width="33.875" bestFit="1" customWidth="1" style="23" min="9" max="9"/>
-    <col width="9.125" customWidth="1" style="23" min="10" max="84"/>
-    <col width="9.125" customWidth="1" style="23" min="85" max="16384"/>
+    <col width="9.125" customWidth="1" style="23" min="10" max="85"/>
+    <col width="9.125" customWidth="1" style="23" min="86" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.4" customHeight="1">
@@ -5561,7 +5561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
     <col width="21.75" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5605,14 +5605,14 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>ba_mai</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>把脉</t>
+      <c r="A2" s="48" t="inlineStr">
+        <is>
+          <t>si_zhen</t>
+        </is>
+      </c>
+      <c r="B2" s="48" t="inlineStr">
+        <is>
+          <t>四诊</t>
         </is>
       </c>
       <c r="C2" s="7" t="n">
@@ -5626,149 +5626,7 @@
       <c r="E2" s="85" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>游戏中人体被划分为表、心、肝、脾、肺、肾六个区域；每个区域由气、血、寒热、湿燥四种属性构成；医者通过把脉确定病位和病性。
-【寸关尺】
-寸、关、尺是脉诊中的三个把脉位置，在手腕桡骨动脉上。医者通过按压这三个位置，感受脉象的强弱、快慢、沉浮、流畅程度，从而推测人体不同区域和脏腑的健康状况。
-【对应脏腑区域】
-浮脉：表
-左寸：心
-左关：肝
-左尺：肾阴
-右寸：肺
-右关：脾
-右尺：肾阳
-【脉象】
-游戏中脉象由波形图表示。
-波峰的高低反映气的强弱；
-波峰越高气滞程度越高，波峰越低气虚程度越高。
-波线的粗细反映血的状态；
-波线越粗血瘀程度越高，波线越细血虚程度越高。
-波宽的宽窄反映湿燥程度；
-波宽越宽越湿，波宽越窄越燥。
-波速的快慢反映寒热程度；
-波速越快越热，波速越慢越寒。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>kai_fang</t>
-        </is>
-      </c>
-      <c r="B3" s="74" t="inlineStr">
-        <is>
-          <t>断病开方</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>huang_di_nei_jing</t>
-        </is>
-      </c>
-      <c r="E3" s="85" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" s="74" t="inlineStr">
-        <is>
-          <t>【断病】
-可以在搜索栏输入疾病名或拼音、拼音首字母快速查找药材。
-【开方】
-点击选中君臣佐使区域，药材栏选取添加药材和药量，左键点击增加，右键减少。可以在搜索栏输入药材名或拼音、拼音首字母快速查找药材。
-【君臣佐使】
-方剂配伍的基本原则，指一个药方里不同药材扮演的不同角色，就像一只分工明确的团队。
-君药：针对主要病症的核心药材，力量最强，用量最大。
-臣药：辅助君药增强疗效，治疗兼带症状。
-佐药：制约君臣药的毒性或烈性，治疗次要症状。
-使药：调和诸药，引导药物直达病位，解毒缓解副作用。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>xing_yi_ji_kao</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>行医记考</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>huang_di_nei_jing</t>
-        </is>
-      </c>
-      <c r="E4" s="85" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>李东璧在行医过程中记录的心得笔记，白天行医时可翻阅笔记查找药材、方剂、疾病。
-在搜索栏输入药材、方剂、疾病的中文名或拼音、拼音首字母可快速查找。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>yu_zhi_fang_ji</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>预制方剂</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>huang_di_nei_jing</t>
-        </is>
-      </c>
-      <c r="E5" s="85" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>现在你可以预制方剂，开方时搜索并选取方剂名，可自动填入该方剂包含的的所有药材及剂量。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="48" t="inlineStr">
-        <is>
-          <t>si_zhen</t>
-        </is>
-      </c>
-      <c r="B6" s="48" t="inlineStr">
-        <is>
-          <t>四诊</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>huang_di_nei_jing</t>
-        </is>
-      </c>
-      <c r="E6" s="85" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="48" t="inlineStr">
+      <c r="F2" s="48" t="inlineStr">
         <is>
           <t>【四诊】
 四诊是中医收集患者病情资料的四种基本诊察方法，包括望诊、闻诊、问诊和切诊。医者通过观察、听闻、询问和触按患者所表现出的各种信息，了解疾病的病因、病位、性质以及正邪盛衰，为辨证和治疗提供依据。
@@ -5789,29 +5647,29 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="74" t="inlineStr">
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="74" t="inlineStr">
         <is>
           <t>ba_gang_bian_zheng</t>
         </is>
       </c>
-      <c r="B7" s="74" t="inlineStr">
+      <c r="B3" s="74" t="inlineStr">
         <is>
           <t>八纲辨证</t>
         </is>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C3" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E7" s="85" t="n">
+      <c r="E3" s="85" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="74" t="inlineStr">
+      <c r="F3" s="74" t="inlineStr">
         <is>
           <t>【八纲辨证】
 八纲辨证是中医分析病情的基本方法。医者通过望、闻、问、切收集症状，再以阴、阳、表、里、寒、热、虚、实八项纲领进行归纳，从而判断疾病的位置、性质以及正邪力量的盛衰。
@@ -5823,29 +5681,29 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="74" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="74" t="inlineStr">
         <is>
           <t>yin_yang</t>
         </is>
       </c>
-      <c r="B8" s="74" t="inlineStr">
+      <c r="B4" s="74" t="inlineStr">
         <is>
           <t>阴阳</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C4" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E8" s="85" t="n">
+      <c r="E4" s="85" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="74" t="inlineStr">
+      <c r="F4" s="74" t="inlineStr">
         <is>
           <t>【阴阳】
 阴阳是中医认识人体与自然变化的基本方法。阴代表相对安静、寒凉、内守的一面，阳代表相对活动、温热、外发的一面。二者相互对立，又彼此依存，并会随着时间与环境不断消长变化。
@@ -5853,29 +5711,29 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>biao_li</t>
         </is>
       </c>
-      <c r="B9" s="74" t="inlineStr">
+      <c r="B5" s="74" t="inlineStr">
         <is>
           <t>表里</t>
         </is>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C5" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E9" s="85" t="n">
+      <c r="E5" s="85" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>【表里】
 表里是中医八纲辨证中用来判断疾病部位深浅和病势进退的两项纲领。表证通常指病邪位于皮毛、肌腠和经络，多见于外邪侵袭人体的初期；里证通常指病邪深入脏腑、气血或骨髓，也可由饮食、情志、劳倦等内伤因素直接形成。这里的表里并不单纯指身体的外部和内部，而是对病位与病势的综合判断。
@@ -5885,29 +5743,29 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>han_re</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>寒热</t>
         </is>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C6" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E10" s="85" t="n">
+      <c r="E6" s="85" t="n">
         <v>5</v>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>【寒热】
 寒热是中医八纲辨证中用来判断疾病性质的两项纲领。寒证多由寒邪侵袭，或人体阳气不足所致；热证多由热邪侵袭、阳气偏盛，或阴液不足所致。这里的寒热并不只指体温高低，而是对患者整体表现的综合判断。
@@ -5917,29 +5775,29 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>xu_shi</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>虚实</t>
         </is>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C7" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E11" s="85" t="n">
+      <c r="E7" s="85" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>【虚实】
 虚实是中医八纲辨证中用来判断人体正气强弱和病邪盛衰的两项纲领。虚证多由人体正气不足、脏腑功能衰退，或气血阴阳亏损所致；实证多由外邪侵袭，或痰饮、瘀血、食积等病理产物壅盛所致。这里的虚实并不单指身体强壮或虚弱，而是对正邪双方力量和病理状态的综合判断。
@@ -5949,29 +5807,29 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="74" t="inlineStr">
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="74" t="inlineStr">
         <is>
           <t>wu_xing</t>
         </is>
       </c>
-      <c r="B12" s="74" t="inlineStr">
+      <c r="B8" s="74" t="inlineStr">
         <is>
           <t>五行</t>
         </is>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C8" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E12" s="85" t="n">
+      <c r="E8" s="85" t="n">
         <v>7</v>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>【五行】
 五行是以木、火、土、金、水五种属性，说明自然与人体之间相互联系、不断变化的规律。五行并非单指五种物质，而是对生长、温热、承载、收敛和滋润等不同特性的概括。
@@ -5994,29 +5852,29 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>zang_xiang</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>藏象</t>
         </is>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C9" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E13" s="85" t="n">
+      <c r="E9" s="85" t="n">
         <v>8</v>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>【藏象】
 藏象是中医研究人体脏腑生理功能、病理变化及其相互关系的理论。“藏”指藏于体内的脏腑，“象”指脏腑功能表现于外的各种征象。中医通过观察人的面色、形体、情志、声音、舌象和脉象等外在变化，推断脏腑的功能状态。
@@ -6025,29 +5883,29 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>gan</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>肝</t>
         </is>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C10" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E14" s="85" t="n">
+      <c r="E10" s="85" t="n">
         <v>9</v>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>【肝】
 肝是五脏之一，在五行属木，与胆相表里。中医认为肝具有主疏泄和藏血的功能。主疏泄是指肝能够调畅全身气机，促进脾胃运化、胆汁排泄和情志活动；藏血是指肝能够贮藏血液，并根据人体活动和休息的需要调节血量。
@@ -6056,29 +5914,29 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>xin</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>心</t>
         </is>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C11" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E15" s="85" t="n">
+      <c r="E11" s="85" t="n">
         <v>10</v>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>【心】
 心是五脏之一，在五行属火，与小肠相表里。中医认为心具有主血脉和藏神的功能。主血脉是指心气推动血液在脉中运行，以濡养全身；藏神是指心与人的精神、意识、思维、情志和睡眠等活动密切相关。
@@ -6087,29 +5945,29 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>pi</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>脾</t>
         </is>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C12" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E16" s="85" t="n">
+      <c r="E12" s="85" t="n">
         <v>11</v>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>【脾】
 脾是五脏之一，在五行属土，与胃相表里。中医认为脾具有主运化、升清和统血的功能。主运化是指脾将饮食物转化为水谷精微，并输布至全身；升清是指将精微物质向上输送；统血是指脾气能够固摄血液，使其正常运行于脉中。
@@ -6118,29 +5976,29 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>fei</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>肺</t>
         </is>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C13" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E17" s="85" t="n">
+      <c r="E13" s="85" t="n">
         <v>12</v>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>【肺】
 肺是五脏之一，在五行属金，与大肠相表里。中医认为肺具有主气、司呼吸、主宣发肃降和通调水道的功能。肺吸入自然界的清气，并参与宗气的生成；宣发使气和津液向上、向外输布，肃降使气和津液向下运行，并维持呼吸通畅。
@@ -6149,29 +6007,29 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>shen</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>肾</t>
         </is>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C14" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E18" s="85" t="n">
+      <c r="E14" s="85" t="n">
         <v>13</v>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>【肾】
 肾是五脏之一，在五行属水，与膀胱相表里。中医认为肾具有藏精、主生长发育与生殖、主水和主纳气的功能。肾精是人体生长、发育和生殖的重要物质基础；肾主水，是指肾参与调节全身水液代谢；肾主纳气，是指肾能够帮助肺维持呼吸的深度和稳定。
@@ -6180,29 +6038,29 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="48" t="inlineStr">
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="48" t="inlineStr">
         <is>
           <t>qi</t>
         </is>
       </c>
-      <c r="B19" s="48" t="inlineStr">
+      <c r="B15" s="48" t="inlineStr">
         <is>
           <t>气</t>
         </is>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C15" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E19" s="85" t="n">
+      <c r="E15" s="85" t="n">
         <v>14</v>
       </c>
-      <c r="F19" s="48" t="inlineStr">
+      <c r="F15" s="48" t="inlineStr">
         <is>
           <t>【气】
 气是中医生命理论中的基本概念，既指构成人体和维持生命活动的精微物质，也指脏腑经络所表现出的功能活动。人体之气主要由先天之精、水谷精微和自然界清气化生，并依靠肺、脾、肾等脏腑共同维持。
@@ -6211,29 +6069,29 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="48" t="inlineStr">
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="48" t="inlineStr">
         <is>
           <t>xue</t>
         </is>
       </c>
-      <c r="B20" s="48" t="inlineStr">
+      <c r="B16" s="48" t="inlineStr">
         <is>
           <t>血</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C16" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E20" s="85" t="n">
+      <c r="E16" s="85" t="n">
         <v>15</v>
       </c>
-      <c r="F20" s="48" t="inlineStr">
+      <c r="F16" s="48" t="inlineStr">
         <is>
           <t>【血】
 血是中医所说运行于脉中、具有濡养和滋润作用的红色液态物质，也是维持人体生命活动的重要基础。血主要由脾胃运化所得的水谷精微化生，并与营气、津液及肾精的作用密切相关。
@@ -6242,29 +6100,29 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="48" t="inlineStr">
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="48" t="inlineStr">
         <is>
           <t>jin</t>
         </is>
       </c>
-      <c r="B21" s="48" t="inlineStr">
+      <c r="B17" s="48" t="inlineStr">
         <is>
           <t>津</t>
         </is>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C17" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E21" s="85" t="n">
+      <c r="E17" s="85" t="n">
         <v>16</v>
       </c>
-      <c r="F21" s="48" t="inlineStr">
+      <c r="F17" s="48" t="inlineStr">
         <is>
           <t>【津】
 津是人体正常水液的一部分，与液合称“津液”。中医认为津的性质较为清稀、流动性较强，主要分布于皮肤、肌肉和孔窍，也可渗入血脉，参与血液的组成和运行。
@@ -6273,29 +6131,29 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="48" t="inlineStr">
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="48" t="inlineStr">
         <is>
           <t>ye</t>
         </is>
       </c>
-      <c r="B22" s="48" t="inlineStr">
+      <c r="B18" s="48" t="inlineStr">
         <is>
           <t>液</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C18" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E22" s="85" t="n">
+      <c r="E18" s="85" t="n">
         <v>17</v>
       </c>
-      <c r="F22" s="48" t="inlineStr">
+      <c r="F18" s="48" t="inlineStr">
         <is>
           <t>【液】
 液是人体正常水液的一部分，与津合称“津液”。中医认为液的性质较为稠厚、流动性相对较小，主要分布于脏腑、关节、骨髓和脑髓等较深部位。
@@ -6304,29 +6162,29 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>wai_gan_liu_xie</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>外感六邪</t>
         </is>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C19" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E23" s="85" t="n">
+      <c r="E19" s="85" t="n">
         <v>18</v>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>【外感六邪】
 外感六邪是中医对风、寒、暑、湿、燥、热六类外来致病因素的统称，又称“六淫”。风、寒、暑、湿、燥、热原本是自然界正常的气候变化，称为“六气”；当气候变化过于强烈、反常，或人体正气不足、适应能力下降时，六气便可能成为致病因素。
@@ -6335,29 +6193,29 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>feng_xie</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>风邪</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C20" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E24" s="85" t="n">
+      <c r="E20" s="85" t="n">
         <v>19</v>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>【风邪】
 风邪是外感六邪之一，在五行与春季相应，但其他季节也可出现。中医认为风为阳邪，性质轻扬开泄，容易侵袭人体上部、肌表和肺卫，因此风邪致病多见头面部及体表症状。
@@ -6366,29 +6224,29 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>han_xie</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>寒邪</t>
         </is>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C21" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E25" s="85" t="n">
+      <c r="E21" s="85" t="n">
         <v>20</v>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>【寒邪】
 寒邪是外感六邪之一，在五行与冬季相应，气温骤降、衣着不足或长时间处于寒冷环境时较易侵袭人体。中医认为寒为阴邪，容易损伤人体阳气，使温煦和推动功能受到影响。
@@ -6397,29 +6255,29 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>shu_xie</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>署邪</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C22" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E26" s="85" t="n">
+      <c r="E22" s="85" t="n">
         <v>21</v>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>【暑邪】
 暑邪是外感六邪之一，是夏季特有的致病邪气，多由天气炎热、长时间暴露于高温环境或劳作过度所致。中医认为暑为阳邪，性质炎热升散，容易使人体腠理开泄、汗液大量排出。
@@ -6428,29 +6286,29 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>shi_xie</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>湿邪</t>
         </is>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C23" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E27" s="85" t="n">
+      <c r="E23" s="85" t="n">
         <v>22</v>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>【湿邪】
 湿邪是外感六邪之一，在五行与长夏相应，常与气候潮湿、淋雨涉水或长期处于湿润环境有关。中医认为湿为阴邪，容易阻碍气机、损伤阳气，并与脾的运化功能关系密切。
@@ -6459,29 +6317,29 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>zao_xie</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>燥邪</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C24" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E28" s="85" t="n">
+      <c r="E24" s="85" t="n">
         <v>23</v>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>【燥邪】
 燥邪是外感六邪之一，在五行与秋季相应，常见于气候干燥或人体津液不足以适应环境变化时。中医认为燥邪性质干涩，最容易耗伤人体津液，并容易侵袭肺脏。
@@ -6490,29 +6348,29 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>re_xie</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>热邪</t>
         </is>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C25" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E29" s="85" t="n">
+      <c r="E25" s="85" t="n">
         <v>24</v>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>【热邪】
 热邪是外感六邪之一，又常称为火邪。中医认为热为阳邪，性质炎热升腾，容易使人体出现阳热偏盛的表现。热邪可由外界侵入，也可由其他邪气在体内转化而成；热邪发展至较严重程度时，常称为火邪。
@@ -6521,29 +6379,29 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>qi_qing_nei_shang</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>七情内伤</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C26" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E30" s="85" t="n">
+      <c r="E26" s="85" t="n">
         <v>25</v>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>【七情内伤】
 七情内伤是中医对喜、怒、忧、思、悲、恐、惊七种情志活动引起疾病的概括。七情原本是人体对外界事物产生的正常情绪反应，一般不会致病；当情绪过于强烈、突然发生或持续时间过长，超过人体自身的调节能力时，便可能影响脏腑气血，成为内伤病因。
@@ -6553,29 +6411,29 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>xi</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>喜</t>
         </is>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C27" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E31" s="85" t="n">
+      <c r="E27" s="85" t="n">
         <v>26</v>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>【喜】
 喜是七情之一，是人在愿望得到满足或遇到愉快事物时产生的正常情绪。适度的喜悦能够使心情舒畅、气血和缓，对身心具有积极作用。中医认为喜与心相应，正常的喜悦有助于心气调畅。
@@ -6584,29 +6442,29 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>nu</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>怒</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C28" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E32" s="85" t="n">
+      <c r="E28" s="85" t="n">
         <v>27</v>
       </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>【怒】
 怒是七情之一，是人在受到挫折、压迫或不公平对待时产生的正常情绪。适度表达愤怒有助于情绪疏解，但长期压抑、频繁发怒或突然暴怒，都可能影响人体气机。
@@ -6615,29 +6473,29 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>you</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>忧</t>
         </is>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C29" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E33" s="85" t="n">
+      <c r="E29" s="85" t="n">
         <v>28</v>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>【忧】
 忧是七情之一，主要指因担心、顾虑或处境不安而产生的忧愁情绪。短暂的忧虑属于正常心理活动，但长期忧心忡忡、反复担忧，则可能使气机受到抑制。
@@ -6646,29 +6504,29 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>si</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>思</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C30" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E34" s="85" t="n">
+      <c r="E30" s="85" t="n">
         <v>29</v>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>【思】
 思是七情之一，主要指思考、谋虑和注意力集中的精神活动。正常思考有助于学习和处理问题，但思虑过度、长期用脑或反复纠结同一件事，则可能影响人体气机。
@@ -6677,29 +6535,29 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>bei</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>悲</t>
         </is>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C31" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E35" s="85" t="n">
+      <c r="E31" s="85" t="n">
         <v>30</v>
       </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>【悲】
 悲是七情之一，是人在经历失去、离别或重大打击时产生的哀伤情绪。适度悲伤属于正常的情感反应，但悲伤过度或长期不能缓解时，可能消耗人体之气，使精神和身体逐渐衰弱。
@@ -6708,29 +6566,29 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>kong</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>恐</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C32" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E36" s="85" t="n">
+      <c r="E32" s="85" t="n">
         <v>31</v>
       </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>【恐】
 恐是七情之一，是人在面临危险、威胁或未知事物时产生的害怕情绪。适度恐惧能够使人提高警觉、躲避危险，但长期处于恐惧之中或突然受到强烈惊吓，则可能扰乱脏腑气机。
@@ -6739,29 +6597,29 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>jing</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>惊</t>
         </is>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C33" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E37" s="85" t="n">
+      <c r="E33" s="85" t="n">
         <v>32</v>
       </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>【惊】
 惊是七情之一，是人在突然遇到意外、声响或危险时产生的急剧情绪反应。惊与恐有所不同：惊通常由突发刺激引起，事先没有心理准备；恐则多是对已知或预期危险产生的害怕。
@@ -6769,6 +6627,38 @@
 惊伤心神时，常见心悸、失眠、神志不宁、精神恍惚、容易受惊或注意力难以集中等表现；情况严重时，还可能出现昏厥或神志异常。判断时需要结合刺激强度、持续影响及患者原有的身心状态综合分析。</t>
         </is>
       </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="7" t="n"/>
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="85" t="n"/>
+      <c r="F34" s="7" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="7" t="n"/>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="85" t="n"/>
+      <c r="F35" s="7" t="n"/>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="7" t="n"/>
+      <c r="B36" s="7" t="n"/>
+      <c r="C36" s="7" t="n"/>
+      <c r="D36" s="7" t="n"/>
+      <c r="E36" s="85" t="n"/>
+      <c r="F36" s="7" t="n"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="7" t="n"/>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="85" t="n"/>
+      <c r="F37" s="7" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="7" t="n"/>
@@ -6839,7 +6729,6 @@
       <c r="B46" s="7" t="n"/>
       <c r="C46" s="7" t="n"/>
       <c r="D46" s="7" t="n"/>
-      <c r="E46" s="85" t="n"/>
       <c r="F46" s="7" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -6847,38 +6736,7 @@
       <c r="B47" s="7" t="n"/>
       <c r="C47" s="7" t="n"/>
       <c r="D47" s="7" t="n"/>
-      <c r="E47" s="85" t="n"/>
       <c r="F47" s="7" t="n"/>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="7" t="n"/>
-      <c r="B48" s="7" t="n"/>
-      <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="n"/>
-      <c r="E48" s="85" t="n"/>
-      <c r="F48" s="7" t="n"/>
-    </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="7" t="n"/>
-      <c r="B49" s="7" t="n"/>
-      <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="n"/>
-      <c r="E49" s="85" t="n"/>
-      <c r="F49" s="7" t="n"/>
-    </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="7" t="n"/>
-      <c r="B50" s="7" t="n"/>
-      <c r="C50" s="7" t="n"/>
-      <c r="D50" s="7" t="n"/>
-      <c r="F50" s="7" t="n"/>
-    </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="7" t="n"/>
-      <c r="B51" s="7" t="n"/>
-      <c r="C51" s="7" t="n"/>
-      <c r="D51" s="7" t="n"/>
-      <c r="F51" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6908,8 +6766,8 @@
     <col width="8.375" bestFit="1" customWidth="1" style="46" min="16" max="18"/>
     <col width="10.75" customWidth="1" style="46" min="19" max="19"/>
     <col width="10" bestFit="1" customWidth="1" style="46" min="20" max="20"/>
-    <col width="9" customWidth="1" style="47" min="21" max="34"/>
-    <col width="9" customWidth="1" style="47" min="35" max="16384"/>
+    <col width="9" customWidth="1" style="47" min="21" max="35"/>
+    <col width="9" customWidth="1" style="47" min="36" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customFormat="1" customHeight="1" s="46">
@@ -9980,8 +9838,8 @@
     <col width="48" customWidth="1" style="10" min="9" max="9"/>
     <col width="150.5" customWidth="1" style="64" min="10" max="10"/>
     <col width="8.875" customWidth="1" style="66" min="11" max="11"/>
-    <col width="8.875" customWidth="1" style="36" min="12" max="58"/>
-    <col width="8.875" customWidth="1" style="36" min="59" max="16384"/>
+    <col width="8.875" customWidth="1" style="36" min="12" max="59"/>
+    <col width="8.875" customWidth="1" style="36" min="60" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29279,8 +29137,8 @@
     <col width="5.125" customWidth="1" style="35" min="27" max="27"/>
     <col width="5" customWidth="1" style="35" min="28" max="28"/>
     <col width="5.25" customWidth="1" style="35" min="29" max="29"/>
-    <col width="9" customWidth="1" style="9" min="30" max="132"/>
-    <col width="9" customWidth="1" style="9" min="133" max="16384"/>
+    <col width="9" customWidth="1" style="9" min="30" max="133"/>
+    <col width="9" customWidth="1" style="9" min="134" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -52302,8 +52160,8 @@
     <cfRule type="duplicateValues" priority="2366" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A77 A79:A100 A102:A106 A114:A1048576">
+    <cfRule type="duplicateValues" priority="2331" dxfId="0"/>
     <cfRule type="duplicateValues" priority="2332" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="2331" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A5">
     <cfRule type="duplicateValues" priority="162" dxfId="0"/>
@@ -52330,32 +52188,32 @@
     <cfRule type="duplicateValues" priority="126" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" priority="123" dxfId="0"/>
     <cfRule type="duplicateValues" priority="124" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="123" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
     <cfRule type="duplicateValues" priority="121" dxfId="0"/>
     <cfRule type="duplicateValues" priority="122" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17">
+    <cfRule type="duplicateValues" priority="119" dxfId="0"/>
     <cfRule type="duplicateValues" priority="120" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="119" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18">
+    <cfRule type="duplicateValues" priority="117" dxfId="0"/>
     <cfRule type="duplicateValues" priority="118" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="117" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:A20">
+    <cfRule type="duplicateValues" priority="115" dxfId="0"/>
     <cfRule type="duplicateValues" priority="116" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="115" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
     <cfRule type="duplicateValues" priority="112" dxfId="0"/>
     <cfRule type="duplicateValues" priority="113" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A26">
+    <cfRule type="duplicateValues" priority="110" dxfId="0"/>
     <cfRule type="duplicateValues" priority="111" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="110" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27">
     <cfRule type="duplicateValues" priority="140" dxfId="0"/>
@@ -52394,20 +52252,20 @@
     <cfRule type="duplicateValues" priority="632" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40">
+    <cfRule type="duplicateValues" priority="154" dxfId="0"/>
     <cfRule type="duplicateValues" priority="155" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="154" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41">
     <cfRule type="duplicateValues" priority="78" dxfId="0"/>
     <cfRule type="duplicateValues" priority="79" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43">
+    <cfRule type="duplicateValues" priority="76" dxfId="0"/>
     <cfRule type="duplicateValues" priority="77" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="76" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44">
+    <cfRule type="duplicateValues" priority="146" dxfId="0"/>
     <cfRule type="duplicateValues" priority="147" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="146" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45">
     <cfRule type="duplicateValues" priority="90" dxfId="0"/>
@@ -52418,8 +52276,8 @@
     <cfRule type="duplicateValues" priority="94" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:A48">
+    <cfRule type="duplicateValues" priority="54" dxfId="0"/>
     <cfRule type="duplicateValues" priority="55" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="54" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:A52">
     <cfRule type="duplicateValues" priority="106" dxfId="0"/>
@@ -52430,32 +52288,32 @@
     <cfRule type="duplicateValues" priority="45" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54">
+    <cfRule type="duplicateValues" priority="28" dxfId="0"/>
     <cfRule type="duplicateValues" priority="29" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="28" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55">
+    <cfRule type="duplicateValues" priority="133" dxfId="0"/>
     <cfRule type="duplicateValues" priority="134" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="133" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56">
+    <cfRule type="duplicateValues" priority="49" dxfId="0"/>
     <cfRule type="duplicateValues" priority="50" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="49" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57">
+    <cfRule type="duplicateValues" priority="148" dxfId="0"/>
     <cfRule type="duplicateValues" priority="149" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="148" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58">
     <cfRule type="duplicateValues" priority="152" dxfId="0"/>
     <cfRule type="duplicateValues" priority="153" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59">
+    <cfRule type="duplicateValues" priority="73" dxfId="0"/>
     <cfRule type="duplicateValues" priority="74" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="73" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A60">
+    <cfRule type="duplicateValues" priority="71" dxfId="0"/>
     <cfRule type="duplicateValues" priority="72" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="71" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61">
     <cfRule type="duplicateValues" priority="86" dxfId="0"/>
@@ -52466,8 +52324,8 @@
     <cfRule type="duplicateValues" priority="70" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63">
+    <cfRule type="duplicateValues" priority="65" dxfId="0"/>
     <cfRule type="duplicateValues" priority="66" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="65" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64">
     <cfRule type="duplicateValues" priority="60" dxfId="0"/>
@@ -52478,8 +52336,8 @@
     <cfRule type="duplicateValues" priority="59" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A66">
+    <cfRule type="duplicateValues" priority="56" dxfId="0"/>
     <cfRule type="duplicateValues" priority="57" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="56" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A67">
     <cfRule type="duplicateValues" priority="150" dxfId="0"/>
@@ -52490,8 +52348,8 @@
     <cfRule type="duplicateValues" priority="866" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69">
+    <cfRule type="duplicateValues" priority="52" dxfId="0"/>
     <cfRule type="duplicateValues" priority="53" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="52" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70">
     <cfRule type="duplicateValues" priority="42" dxfId="0"/>
@@ -52502,36 +52360,36 @@
     <cfRule type="duplicateValues" priority="10" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A72:A73">
+    <cfRule type="duplicateValues" priority="99" dxfId="0"/>
     <cfRule type="duplicateValues" priority="100" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="99" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A74">
     <cfRule type="duplicateValues" priority="95" dxfId="0"/>
     <cfRule type="duplicateValues" priority="96" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A75:A77">
+    <cfRule type="duplicateValues" priority="38" dxfId="0"/>
     <cfRule type="duplicateValues" priority="39" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="38" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A78">
+    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
     <cfRule type="duplicateValues" priority="2" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A79 A106">
     <cfRule type="duplicateValues" priority="1727" dxfId="0"/>
     <cfRule type="duplicateValues" priority="1728" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A80">
+    <cfRule type="duplicateValues" priority="62" dxfId="0"/>
     <cfRule type="duplicateValues" priority="63" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="62" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A82:A83">
     <cfRule type="duplicateValues" priority="982" dxfId="0"/>
     <cfRule type="duplicateValues" priority="983" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A84">
+    <cfRule type="duplicateValues" priority="135" dxfId="0"/>
     <cfRule type="duplicateValues" priority="136" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="135" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A85">
     <cfRule type="duplicateValues" priority="13" dxfId="0"/>
@@ -52562,12 +52420,12 @@
     <cfRule type="duplicateValues" priority="41" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A96">
+    <cfRule type="duplicateValues" priority="84" dxfId="0"/>
     <cfRule type="duplicateValues" priority="85" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="84" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A98">
+    <cfRule type="duplicateValues" priority="16" dxfId="0"/>
     <cfRule type="duplicateValues" priority="17" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="16" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A99">
     <cfRule type="duplicateValues" priority="26" dxfId="0"/>
@@ -52582,12 +52440,12 @@
     <cfRule type="duplicateValues" priority="4" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A102">
+    <cfRule type="duplicateValues" priority="88" dxfId="0"/>
     <cfRule type="duplicateValues" priority="89" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="88" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A103">
+    <cfRule type="duplicateValues" priority="142" dxfId="0"/>
     <cfRule type="duplicateValues" priority="143" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="142" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A104:A105">
     <cfRule type="duplicateValues" priority="1709" dxfId="0"/>
@@ -52598,8 +52456,8 @@
     <cfRule type="duplicateValues" priority="1944" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A114:A115">
+    <cfRule type="duplicateValues" priority="131" dxfId="0"/>
     <cfRule type="duplicateValues" priority="132" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="131" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A117:A1048576">
     <cfRule type="duplicateValues" priority="395" dxfId="0"/>

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="3" activeTab="9" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" state="visible" r:id="rId1"/>
@@ -2417,8 +2417,8 @@
     <col width="25.5" bestFit="1" customWidth="1" style="23" min="7" max="7"/>
     <col width="31.75" bestFit="1" customWidth="1" style="23" min="8" max="8"/>
     <col width="33.875" bestFit="1" customWidth="1" style="23" min="9" max="9"/>
-    <col width="9.125" customWidth="1" style="23" min="10" max="85"/>
-    <col width="9.125" customWidth="1" style="23" min="86" max="16384"/>
+    <col width="9.125" customWidth="1" style="23" min="10" max="86"/>
+    <col width="9.125" customWidth="1" style="23" min="87" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.4" customHeight="1">
@@ -6766,8 +6766,8 @@
     <col width="8.375" bestFit="1" customWidth="1" style="46" min="16" max="18"/>
     <col width="10.75" customWidth="1" style="46" min="19" max="19"/>
     <col width="10" bestFit="1" customWidth="1" style="46" min="20" max="20"/>
-    <col width="9" customWidth="1" style="47" min="21" max="35"/>
-    <col width="9" customWidth="1" style="47" min="36" max="16384"/>
+    <col width="9" customWidth="1" style="47" min="21" max="36"/>
+    <col width="9" customWidth="1" style="47" min="37" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customFormat="1" customHeight="1" s="46">
@@ -7466,9 +7466,7 @@
       <c r="O14" s="48" t="inlineStr"/>
       <c r="P14" s="48" t="inlineStr"/>
       <c r="Q14" s="48" t="inlineStr"/>
-      <c r="R14" s="48" t="n">
-        <v>5</v>
-      </c>
+      <c r="R14" s="48" t="inlineStr"/>
       <c r="S14" s="48" t="b">
         <v>1</v>
       </c>
@@ -7574,9 +7572,7 @@
       <c r="O16" s="48" t="inlineStr"/>
       <c r="P16" s="48" t="inlineStr"/>
       <c r="Q16" s="48" t="inlineStr"/>
-      <c r="R16" s="48" t="n">
-        <v>5</v>
-      </c>
+      <c r="R16" s="48" t="inlineStr"/>
       <c r="S16" s="48" t="b">
         <v>1</v>
       </c>
@@ -7678,9 +7674,7 @@
       <c r="Q18" s="48" t="n">
         <v>1000</v>
       </c>
-      <c r="R18" s="48" t="n">
-        <v>5</v>
-      </c>
+      <c r="R18" s="48" t="inlineStr"/>
       <c r="S18" s="48" t="b">
         <v>1</v>
       </c>
@@ -9419,7 +9413,7 @@
         </is>
       </c>
       <c r="D53" s="48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E53" s="48" t="inlineStr"/>
       <c r="F53" s="48" t="inlineStr"/>
@@ -9428,7 +9422,7 @@
       <c r="I53" s="48" t="inlineStr"/>
       <c r="J53" s="48" t="inlineStr">
         <is>
-          <t>008_02</t>
+          <t>024_02</t>
         </is>
       </c>
       <c r="K53" s="48" t="inlineStr"/>
@@ -9443,7 +9437,7 @@
       <c r="P53" s="48" t="inlineStr"/>
       <c r="Q53" s="48" t="inlineStr"/>
       <c r="R53" s="48" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S53" s="48" t="b">
         <v>1</v>
@@ -9838,8 +9832,8 @@
     <col width="48" customWidth="1" style="10" min="9" max="9"/>
     <col width="150.5" customWidth="1" style="64" min="10" max="10"/>
     <col width="8.875" customWidth="1" style="66" min="11" max="11"/>
-    <col width="8.875" customWidth="1" style="36" min="12" max="59"/>
-    <col width="8.875" customWidth="1" style="36" min="60" max="16384"/>
+    <col width="8.875" customWidth="1" style="36" min="12" max="60"/>
+    <col width="8.875" customWidth="1" style="36" min="61" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24635,38 +24629,54 @@
       </c>
       <c r="K373" s="50" t="inlineStr"/>
     </row>
-    <row r="374">
-      <c r="A374" s="55" t="inlineStr">
-        <is>
-          <t>024_04</t>
-        </is>
-      </c>
-      <c r="B374" s="55" t="inlineStr">
-        <is>
-          <t>王百堂来访</t>
-        </is>
-      </c>
-      <c r="C374" s="55" t="n">
-        <v>6</v>
+    <row r="374" ht="34.5" customHeight="1">
+      <c r="A374" s="50" t="inlineStr">
+        <is>
+          <t>025_01</t>
+        </is>
+      </c>
+      <c r="B374" s="50" t="inlineStr">
+        <is>
+          <t>和尚肾精不足</t>
+        </is>
+      </c>
+      <c r="C374" s="50" t="n">
+        <v>1</v>
       </c>
       <c r="D374" s="50" t="inlineStr">
         <is>
-          <t>subtitle</t>
-        </is>
-      </c>
-      <c r="E374" s="55" t="inlineStr"/>
-      <c r="F374" s="51" t="inlineStr"/>
-      <c r="G374" s="55" t="inlineStr"/>
-      <c r="H374" s="55" t="inlineStr"/>
-      <c r="I374" s="55" t="inlineStr"/>
-      <c r="J374" s="55" t="inlineStr">
-        <is>
-          <t>心得+5</t>
-        </is>
-      </c>
-      <c r="K374" s="55" t="inlineStr"/>
-    </row>
-    <row r="375" ht="34.5" customHeight="1">
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E374" s="50" t="inlineStr">
+        <is>
+          <t>性空</t>
+        </is>
+      </c>
+      <c r="F374" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G374" s="51" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
+      <c r="H374" s="52" t="inlineStr"/>
+      <c r="I374" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J374" s="67" t="inlineStr">
+        <is>
+          <t>阿弥陀佛，贫僧法号性空，《中论》曰："众因缘生法，我说即是空，亦为是假名，亦是中道义。"正所谓缘起性空是也。</t>
+        </is>
+      </c>
+      <c r="K374" s="50" t="inlineStr"/>
+    </row>
+    <row r="375">
       <c r="A375" s="50" t="inlineStr">
         <is>
           <t>025_01</t>
@@ -24678,7 +24688,7 @@
         </is>
       </c>
       <c r="C375" s="50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D375" s="50" t="inlineStr">
         <is>
@@ -24687,28 +24697,20 @@
       </c>
       <c r="E375" s="50" t="inlineStr">
         <is>
-          <t>性空</t>
-        </is>
-      </c>
-      <c r="F375" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G375" s="51" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F375" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G375" s="51" t="inlineStr"/>
       <c r="H375" s="52" t="inlineStr"/>
-      <c r="I375" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
+      <c r="I375" s="51" t="inlineStr"/>
       <c r="J375" s="67" t="inlineStr">
         <is>
-          <t>阿弥陀佛，贫僧法号性空，《中论》曰："众因缘生法，我说即是空，亦为是假名，亦是中道义。"正所谓缘起性空是也。</t>
+          <t>师父请坐，今日来小馆是？(这和尚身上好大的酒味啊...)</t>
         </is>
       </c>
       <c r="K375" s="50" t="inlineStr"/>
@@ -24725,7 +24727,7 @@
         </is>
       </c>
       <c r="C376" s="50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D376" s="50" t="inlineStr">
         <is>
@@ -24734,20 +24736,24 @@
       </c>
       <c r="E376" s="50" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F376" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G376" s="51" t="inlineStr"/>
+          <t>性空</t>
+        </is>
+      </c>
+      <c r="F376" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G376" s="51" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
       <c r="H376" s="52" t="inlineStr"/>
       <c r="I376" s="51" t="inlineStr"/>
-      <c r="J376" s="67" t="inlineStr">
-        <is>
-          <t>师父请坐，今日来小馆是？(这和尚身上好大的酒味啊...)</t>
+      <c r="J376" s="50" t="inlineStr">
+        <is>
+          <t>最近身体不太舒服，老是耳鸣头晕，请大夫给贫僧看看。</t>
         </is>
       </c>
       <c r="K376" s="50" t="inlineStr"/>
@@ -24755,16 +24761,16 @@
     <row r="377">
       <c r="A377" s="50" t="inlineStr">
         <is>
-          <t>025_01</t>
+          <t>025_02</t>
         </is>
       </c>
       <c r="B377" s="50" t="inlineStr">
         <is>
-          <t>和尚肾精不足</t>
+          <t>025治疗成功</t>
         </is>
       </c>
       <c r="C377" s="50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D377" s="50" t="inlineStr">
         <is>
@@ -24773,24 +24779,24 @@
       </c>
       <c r="E377" s="50" t="inlineStr">
         <is>
-          <t>性空</t>
-        </is>
-      </c>
-      <c r="F377" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G377" s="51" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F377" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G377" s="51" t="inlineStr"/>
       <c r="H377" s="52" t="inlineStr"/>
-      <c r="I377" s="51" t="inlineStr"/>
-      <c r="J377" s="50" t="inlineStr">
-        <is>
-          <t>最近身体不太舒服，老是耳鸣头晕，请大夫给贫僧看看。</t>
+      <c r="I377" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J377" s="67" t="inlineStr">
+        <is>
+          <t>师父所患的乃是肾精不足之症，嗯…是房事过劳所致…</t>
         </is>
       </c>
       <c r="K377" s="50" t="inlineStr"/>
@@ -24807,7 +24813,7 @@
         </is>
       </c>
       <c r="C378" s="50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D378" s="50" t="inlineStr">
         <is>
@@ -24816,24 +24822,24 @@
       </c>
       <c r="E378" s="50" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F378" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G378" s="51" t="inlineStr"/>
+          <t>性空</t>
+        </is>
+      </c>
+      <c r="F378" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G378" s="51" t="inlineStr">
+        <is>
+          <t>after</t>
+        </is>
+      </c>
       <c r="H378" s="52" t="inlineStr"/>
-      <c r="I378" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J378" s="67" t="inlineStr">
-        <is>
-          <t>师父所患的乃是肾精不足之症，嗯…是房事过劳所致…</t>
+      <c r="I378" s="51" t="inlineStr"/>
+      <c r="J378" s="50" t="inlineStr">
+        <is>
+          <t>哎哟，施主啊，这可不敢乱说啊，我可是出家人啊，怎么会干那种事呢。</t>
         </is>
       </c>
       <c r="K378" s="50" t="inlineStr"/>
@@ -24850,7 +24856,7 @@
         </is>
       </c>
       <c r="C379" s="50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D379" s="50" t="inlineStr">
         <is>
@@ -24859,24 +24865,20 @@
       </c>
       <c r="E379" s="50" t="inlineStr">
         <is>
-          <t>性空</t>
-        </is>
-      </c>
-      <c r="F379" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G379" s="51" t="inlineStr">
-        <is>
-          <t>after</t>
-        </is>
-      </c>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F379" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G379" s="51" t="inlineStr"/>
       <c r="H379" s="52" t="inlineStr"/>
       <c r="I379" s="51" t="inlineStr"/>
       <c r="J379" s="50" t="inlineStr">
         <is>
-          <t>哎哟，施主啊，这可不敢乱说啊，我可是出家人啊，怎么会干那种事呢。</t>
+          <t>…</t>
         </is>
       </c>
       <c r="K379" s="50" t="inlineStr"/>
@@ -24893,7 +24895,7 @@
         </is>
       </c>
       <c r="C380" s="50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D380" s="50" t="inlineStr">
         <is>
@@ -24902,20 +24904,24 @@
       </c>
       <c r="E380" s="50" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F380" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G380" s="51" t="inlineStr"/>
-      <c r="H380" s="52" t="inlineStr"/>
+          <t>性空</t>
+        </is>
+      </c>
+      <c r="F380" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G380" s="51" t="inlineStr">
+        <is>
+          <t>after</t>
+        </is>
+      </c>
+      <c r="H380" s="51" t="inlineStr"/>
       <c r="I380" s="51" t="inlineStr"/>
       <c r="J380" s="50" t="inlineStr">
         <is>
-          <t>…</t>
+          <t>一定是我晚上念经太过用功，着凉了。</t>
         </is>
       </c>
       <c r="K380" s="50" t="inlineStr"/>
@@ -24932,7 +24938,7 @@
         </is>
       </c>
       <c r="C381" s="50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D381" s="50" t="inlineStr">
         <is>
@@ -24941,24 +24947,20 @@
       </c>
       <c r="E381" s="50" t="inlineStr">
         <is>
-          <t>性空</t>
-        </is>
-      </c>
-      <c r="F381" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G381" s="51" t="inlineStr">
-        <is>
-          <t>after</t>
-        </is>
-      </c>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F381" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G381" s="51" t="inlineStr"/>
       <c r="H381" s="51" t="inlineStr"/>
       <c r="I381" s="51" t="inlineStr"/>
       <c r="J381" s="50" t="inlineStr">
         <is>
-          <t>一定是我晚上念经太过用功，着凉了。</t>
+          <t>是是是，师父说得对，也不是没有这个可能。</t>
         </is>
       </c>
       <c r="K381" s="50" t="inlineStr"/>
@@ -24975,7 +24977,7 @@
         </is>
       </c>
       <c r="C382" s="50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D382" s="50" t="inlineStr">
         <is>
@@ -24984,20 +24986,28 @@
       </c>
       <c r="E382" s="50" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F382" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G382" s="51" t="inlineStr"/>
-      <c r="H382" s="51" t="inlineStr"/>
-      <c r="I382" s="51" t="inlineStr"/>
-      <c r="J382" s="50" t="inlineStr">
-        <is>
-          <t>是是是，师父说得对，也不是没有这个可能。</t>
+          <t>性空</t>
+        </is>
+      </c>
+      <c r="F382" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G382" s="51" t="inlineStr">
+        <is>
+          <t>after</t>
+        </is>
+      </c>
+      <c r="H382" s="55" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
+      <c r="I382" s="55" t="inlineStr"/>
+      <c r="J382" s="73" t="inlineStr">
+        <is>
+          <t>嗯，可别到处乱说啊，这钱你拿着吧，这小郎中真是…</t>
         </is>
       </c>
       <c r="K382" s="50" t="inlineStr"/>
@@ -25014,37 +25024,21 @@
         </is>
       </c>
       <c r="C383" s="50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D383" s="50" t="inlineStr">
         <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E383" s="50" t="inlineStr">
-        <is>
-          <t>性空</t>
-        </is>
-      </c>
-      <c r="F383" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G383" s="51" t="inlineStr">
-        <is>
-          <t>after</t>
-        </is>
-      </c>
-      <c r="H383" s="55" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E383" s="50" t="inlineStr"/>
+      <c r="F383" s="51" t="inlineStr"/>
+      <c r="G383" s="51" t="inlineStr"/>
+      <c r="H383" s="55" t="inlineStr"/>
       <c r="I383" s="55" t="inlineStr"/>
-      <c r="J383" s="73" t="inlineStr">
-        <is>
-          <t>嗯，可别到处乱说啊，这钱你拿着吧，这小郎中真是…</t>
+      <c r="J383" s="56" t="inlineStr">
+        <is>
+          <t>金钱+2两</t>
         </is>
       </c>
       <c r="K383" s="50" t="inlineStr"/>
@@ -25061,21 +25055,29 @@
         </is>
       </c>
       <c r="C384" s="50" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D384" s="50" t="inlineStr">
         <is>
-          <t>subtitle</t>
-        </is>
-      </c>
-      <c r="E384" s="50" t="inlineStr"/>
-      <c r="F384" s="51" t="inlineStr"/>
-      <c r="G384" s="51" t="inlineStr"/>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E384" s="55" t="inlineStr">
+        <is>
+          <t>半夏</t>
+        </is>
+      </c>
+      <c r="F384" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G384" s="55" t="inlineStr"/>
       <c r="H384" s="55" t="inlineStr"/>
       <c r="I384" s="55" t="inlineStr"/>
-      <c r="J384" s="56" t="inlineStr">
-        <is>
-          <t>金钱+2两</t>
+      <c r="J384" s="55" t="inlineStr">
+        <is>
+          <t>哇，这就是传说中的花和尚吗？</t>
         </is>
       </c>
       <c r="K384" s="50" t="inlineStr"/>
@@ -25092,21 +25094,21 @@
         </is>
       </c>
       <c r="C385" s="50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D385" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E385" s="55" t="inlineStr">
-        <is>
-          <t>半夏</t>
+      <c r="E385" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F385" s="52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G385" s="55" t="inlineStr"/>
@@ -25114,7 +25116,7 @@
       <c r="I385" s="55" t="inlineStr"/>
       <c r="J385" s="55" t="inlineStr">
         <is>
-          <t>哇，这就是传说中的花和尚吗？</t>
+          <t>…</t>
         </is>
       </c>
       <c r="K385" s="50" t="inlineStr"/>
@@ -25131,21 +25133,21 @@
         </is>
       </c>
       <c r="C386" s="50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D386" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E386" s="50" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F386" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
+      <c r="E386" s="55" t="inlineStr">
+        <is>
+          <t>陈皮</t>
+        </is>
+      </c>
+      <c r="F386" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G386" s="55" t="inlineStr"/>
@@ -25153,7 +25155,7 @@
       <c r="I386" s="55" t="inlineStr"/>
       <c r="J386" s="55" t="inlineStr">
         <is>
-          <t>…</t>
+          <t>他是花和尚，你是花痴，正好凑一对儿。</t>
         </is>
       </c>
       <c r="K386" s="50" t="inlineStr"/>
@@ -25170,7 +25172,7 @@
         </is>
       </c>
       <c r="C387" s="50" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D387" s="50" t="inlineStr">
         <is>
@@ -25179,12 +25181,12 @@
       </c>
       <c r="E387" s="55" t="inlineStr">
         <is>
-          <t>陈皮</t>
-        </is>
-      </c>
-      <c r="F387" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>半夏</t>
+        </is>
+      </c>
+      <c r="F387" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G387" s="55" t="inlineStr"/>
@@ -25192,7 +25194,7 @@
       <c r="I387" s="55" t="inlineStr"/>
       <c r="J387" s="55" t="inlineStr">
         <is>
-          <t>他是花和尚，你是花痴，正好凑一对儿。</t>
+          <t>找打！</t>
         </is>
       </c>
       <c r="K387" s="50" t="inlineStr"/>
@@ -25209,7 +25211,7 @@
         </is>
       </c>
       <c r="C388" s="50" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D388" s="50" t="inlineStr">
         <is>
@@ -25218,12 +25220,12 @@
       </c>
       <c r="E388" s="55" t="inlineStr">
         <is>
-          <t>半夏</t>
-        </is>
-      </c>
-      <c r="F388" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>陈皮</t>
+        </is>
+      </c>
+      <c r="F388" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G388" s="55" t="inlineStr"/>
@@ -25231,7 +25233,7 @@
       <c r="I388" s="55" t="inlineStr"/>
       <c r="J388" s="55" t="inlineStr">
         <is>
-          <t>找打！</t>
+          <t>哎哟！</t>
         </is>
       </c>
       <c r="K388" s="50" t="inlineStr"/>
@@ -25239,38 +25241,42 @@
     <row r="389">
       <c r="A389" s="50" t="inlineStr">
         <is>
-          <t>025_02</t>
+          <t>025_03</t>
         </is>
       </c>
       <c r="B389" s="50" t="inlineStr">
         <is>
-          <t>025治疗成功</t>
+          <t>025治疗失败</t>
         </is>
       </c>
       <c r="C389" s="50" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D389" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E389" s="55" t="inlineStr">
-        <is>
-          <t>陈皮</t>
-        </is>
-      </c>
-      <c r="F389" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G389" s="55" t="inlineStr"/>
-      <c r="H389" s="55" t="inlineStr"/>
-      <c r="I389" s="55" t="inlineStr"/>
-      <c r="J389" s="55" t="inlineStr">
-        <is>
-          <t>哎哟！</t>
+      <c r="E389" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F389" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G389" s="51" t="inlineStr"/>
+      <c r="H389" s="52" t="inlineStr"/>
+      <c r="I389" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J389" s="50" t="inlineStr">
+        <is>
+          <t>虽然这不是个正经和尚，但还是得好好想想他得的是什么病。</t>
         </is>
       </c>
       <c r="K389" s="50" t="inlineStr"/>
@@ -25278,12 +25284,12 @@
     <row r="390">
       <c r="A390" s="50" t="inlineStr">
         <is>
-          <t>025_03</t>
+          <t>026_01</t>
         </is>
       </c>
       <c r="B390" s="50" t="inlineStr">
         <is>
-          <t>025治疗失败</t>
+          <t>吴芷兰妊娠</t>
         </is>
       </c>
       <c r="C390" s="50" t="n">
@@ -25294,14 +25300,14 @@
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E390" s="50" t="inlineStr">
-        <is>
-          <t>李东璧</t>
+      <c r="E390" s="53" t="inlineStr">
+        <is>
+          <t>半夏</t>
         </is>
       </c>
       <c r="F390" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G390" s="51" t="inlineStr"/>
@@ -25311,9 +25317,9 @@
           <t>current_scene</t>
         </is>
       </c>
-      <c r="J390" s="50" t="inlineStr">
-        <is>
-          <t>虽然这不是个正经和尚，但还是得好好想想他得的是什么病。</t>
+      <c r="J390" s="53" t="inlineStr">
+        <is>
+          <t>少掌柜的，少夫人在屋里晕倒了，您快来看看啊！</t>
         </is>
       </c>
       <c r="K390" s="50" t="inlineStr"/>
@@ -25330,7 +25336,7 @@
         </is>
       </c>
       <c r="C391" s="50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D391" s="50" t="inlineStr">
         <is>
@@ -25339,24 +25345,20 @@
       </c>
       <c r="E391" s="53" t="inlineStr">
         <is>
-          <t>半夏</t>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F391" s="52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G391" s="51" t="inlineStr"/>
       <c r="H391" s="52" t="inlineStr"/>
-      <c r="I391" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
+      <c r="I391" s="51" t="inlineStr"/>
       <c r="J391" s="53" t="inlineStr">
         <is>
-          <t>少掌柜的，少夫人在屋里晕倒了，您快来看看啊！</t>
+          <t>芷兰！！！</t>
         </is>
       </c>
       <c r="K391" s="50" t="inlineStr"/>
@@ -25373,7 +25375,7 @@
         </is>
       </c>
       <c r="C392" s="50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D392" s="50" t="inlineStr">
         <is>
@@ -25382,20 +25384,28 @@
       </c>
       <c r="E392" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
+          <t>吴芷兰</t>
         </is>
       </c>
       <c r="F392" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G392" s="51" t="inlineStr"/>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G392" s="51" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
       <c r="H392" s="52" t="inlineStr"/>
-      <c r="I392" s="51" t="inlineStr"/>
+      <c r="I392" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/026/026.png</t>
+        </is>
+      </c>
       <c r="J392" s="53" t="inlineStr">
         <is>
-          <t>芷兰！！！</t>
+          <t>…...</t>
         </is>
       </c>
       <c r="K392" s="50" t="inlineStr"/>
@@ -25412,7 +25422,7 @@
         </is>
       </c>
       <c r="C393" s="50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D393" s="50" t="inlineStr">
         <is>
@@ -25435,14 +25445,10 @@
         </is>
       </c>
       <c r="H393" s="52" t="inlineStr"/>
-      <c r="I393" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/026/026.png</t>
-        </is>
-      </c>
+      <c r="I393" s="51" t="inlineStr"/>
       <c r="J393" s="53" t="inlineStr">
         <is>
-          <t>…...</t>
+          <t>相公，我最近头晕目眩，时不时的还恶心想吐，不知是怎么了…</t>
         </is>
       </c>
       <c r="K393" s="50" t="inlineStr"/>
@@ -25459,7 +25465,7 @@
         </is>
       </c>
       <c r="C394" s="50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D394" s="50" t="inlineStr">
         <is>
@@ -25468,24 +25474,20 @@
       </c>
       <c r="E394" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F394" s="52" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G394" s="51" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
-      <c r="H394" s="52" t="inlineStr"/>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G394" s="51" t="inlineStr"/>
+      <c r="H394" s="51" t="inlineStr"/>
       <c r="I394" s="51" t="inlineStr"/>
       <c r="J394" s="53" t="inlineStr">
         <is>
-          <t>相公，我最近头晕目眩，时不时的还恶心想吐，不知是怎么了…</t>
+          <t>夫人一定是操持家务太过劳累，我给你把把脉。</t>
         </is>
       </c>
       <c r="K394" s="50" t="inlineStr"/>
@@ -25493,38 +25495,42 @@
     <row r="395">
       <c r="A395" s="50" t="inlineStr">
         <is>
-          <t>026_01</t>
+          <t>026_02</t>
         </is>
       </c>
       <c r="B395" s="50" t="inlineStr">
         <is>
-          <t>吴芷兰妊娠</t>
+          <t>026治疗成功</t>
         </is>
       </c>
       <c r="C395" s="50" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D395" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E395" s="53" t="inlineStr">
-        <is>
-          <t>李东璧</t>
+      <c r="E395" s="50" t="inlineStr">
+        <is>
+          <t>半夏</t>
         </is>
       </c>
       <c r="F395" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G395" s="51" t="inlineStr"/>
-      <c r="H395" s="51" t="inlineStr"/>
-      <c r="I395" s="51" t="inlineStr"/>
-      <c r="J395" s="53" t="inlineStr">
-        <is>
-          <t>夫人一定是操持家务太过劳累，我给你把把脉。</t>
+      <c r="H395" s="52" t="inlineStr"/>
+      <c r="I395" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/026/026.png</t>
+        </is>
+      </c>
+      <c r="J395" s="67" t="inlineStr">
+        <is>
+          <t>呜呜呜，少夫人到底是得了什么病啊。</t>
         </is>
       </c>
       <c r="K395" s="50" t="inlineStr"/>
@@ -25541,7 +25547,7 @@
         </is>
       </c>
       <c r="C396" s="50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D396" s="50" t="inlineStr">
         <is>
@@ -25550,24 +25556,20 @@
       </c>
       <c r="E396" s="50" t="inlineStr">
         <is>
-          <t>半夏</t>
-        </is>
-      </c>
-      <c r="F396" s="52" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F396" s="51" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G396" s="51" t="inlineStr"/>
       <c r="H396" s="52" t="inlineStr"/>
-      <c r="I396" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/026/026.png</t>
-        </is>
-      </c>
-      <c r="J396" s="67" t="inlineStr">
-        <is>
-          <t>呜呜呜，少夫人到底是得了什么病啊。</t>
+      <c r="I396" s="51" t="inlineStr"/>
+      <c r="J396" s="50" t="inlineStr">
+        <is>
+          <t>芷兰…我们有孩子了…</t>
         </is>
       </c>
       <c r="K396" s="50" t="inlineStr"/>
@@ -25584,7 +25586,7 @@
         </is>
       </c>
       <c r="C397" s="50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D397" s="50" t="inlineStr">
         <is>
@@ -25593,12 +25595,12 @@
       </c>
       <c r="E397" s="50" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F397" s="51" t="inlineStr">
-        <is>
-          <t>mid</t>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F397" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G397" s="51" t="inlineStr"/>
@@ -25606,7 +25608,7 @@
       <c r="I397" s="51" t="inlineStr"/>
       <c r="J397" s="50" t="inlineStr">
         <is>
-          <t>芷兰…我们有孩子了…</t>
+          <t>真的吗！哎呀，太好了，是男孩儿女孩儿？</t>
         </is>
       </c>
       <c r="K397" s="50" t="inlineStr"/>
@@ -25623,7 +25625,7 @@
         </is>
       </c>
       <c r="C398" s="50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D398" s="50" t="inlineStr">
         <is>
@@ -25632,20 +25634,20 @@
       </c>
       <c r="E398" s="50" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
-        </is>
-      </c>
-      <c r="F398" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F398" s="51" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G398" s="51" t="inlineStr"/>
-      <c r="H398" s="52" t="inlineStr"/>
+      <c r="H398" s="51" t="inlineStr"/>
       <c r="I398" s="51" t="inlineStr"/>
-      <c r="J398" s="50" t="inlineStr">
-        <is>
-          <t>真的吗！哎呀，太好了，是男孩儿女孩儿？</t>
+      <c r="J398" s="67" t="inlineStr">
+        <is>
+          <t>现在还看不出来，男孩儿女孩儿都一样，我们要当爹当娘了。</t>
         </is>
       </c>
       <c r="K398" s="50" t="inlineStr"/>
@@ -25662,7 +25664,7 @@
         </is>
       </c>
       <c r="C399" s="50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D399" s="50" t="inlineStr">
         <is>
@@ -25671,20 +25673,20 @@
       </c>
       <c r="E399" s="50" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F399" s="51" t="inlineStr">
-        <is>
-          <t>mid</t>
+          <t>半夏</t>
+        </is>
+      </c>
+      <c r="F399" s="52" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G399" s="51" t="inlineStr"/>
       <c r="H399" s="51" t="inlineStr"/>
       <c r="I399" s="51" t="inlineStr"/>
-      <c r="J399" s="67" t="inlineStr">
-        <is>
-          <t>现在还看不出来，男孩儿女孩儿都一样，我们要当爹当娘了。</t>
+      <c r="J399" s="50" t="inlineStr">
+        <is>
+          <t>哇，恭喜恭喜，真是菩萨保佑，我去把这喜事告诉老爷去！</t>
         </is>
       </c>
       <c r="K399" s="50" t="inlineStr"/>
@@ -25692,16 +25694,16 @@
     <row r="400">
       <c r="A400" s="50" t="inlineStr">
         <is>
-          <t>026_02</t>
+          <t>026_03</t>
         </is>
       </c>
       <c r="B400" s="50" t="inlineStr">
         <is>
-          <t>026治疗成功</t>
+          <t>026治疗失败</t>
         </is>
       </c>
       <c r="C400" s="50" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D400" s="50" t="inlineStr">
         <is>
@@ -25710,20 +25712,24 @@
       </c>
       <c r="E400" s="50" t="inlineStr">
         <is>
-          <t>半夏</t>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F400" s="52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G400" s="51" t="inlineStr"/>
-      <c r="H400" s="51" t="inlineStr"/>
-      <c r="I400" s="51" t="inlineStr"/>
+      <c r="H400" s="52" t="inlineStr"/>
+      <c r="I400" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/026/026.png</t>
+        </is>
+      </c>
       <c r="J400" s="50" t="inlineStr">
         <is>
-          <t>哇，恭喜恭喜，真是菩萨保佑，我去把这喜事告诉老爷去！</t>
+          <t>不对不对，我在干什么呀，冷静冷静，再好好想想。</t>
         </is>
       </c>
       <c r="K400" s="50" t="inlineStr"/>
@@ -25731,12 +25737,12 @@
     <row r="401">
       <c r="A401" s="50" t="inlineStr">
         <is>
-          <t>026_03</t>
+          <t>027</t>
         </is>
       </c>
       <c r="B401" s="50" t="inlineStr">
         <is>
-          <t>026治疗失败</t>
+          <t>上元灯节</t>
         </is>
       </c>
       <c r="C401" s="50" t="n">
@@ -25747,9 +25753,9 @@
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E401" s="50" t="inlineStr">
-        <is>
-          <t>李东璧</t>
+      <c r="E401" s="53" t="inlineStr">
+        <is>
+          <t>李言闻</t>
         </is>
       </c>
       <c r="F401" s="52" t="inlineStr">
@@ -25758,18 +25764,22 @@
         </is>
       </c>
       <c r="G401" s="51" t="inlineStr"/>
-      <c r="H401" s="52" t="inlineStr"/>
+      <c r="H401" s="54" t="inlineStr"/>
       <c r="I401" s="51" t="inlineStr">
         <is>
-          <t>res://Assets/Background/026/026.png</t>
-        </is>
-      </c>
-      <c r="J401" s="50" t="inlineStr">
-        <is>
-          <t>不对不对，我在干什么呀，冷静冷静，再好好想想。</t>
-        </is>
-      </c>
-      <c r="K401" s="50" t="inlineStr"/>
+          <t>res://Assets/Background/004/004.png</t>
+        </is>
+      </c>
+      <c r="J401" s="53" t="inlineStr">
+        <is>
+          <t>今天是上元佳节，咱们全家去城里逛逛，听说今年的灯节格外热闹。</t>
+        </is>
+      </c>
+      <c r="K401" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Music/Story/027/元宵夜樂.mp3</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="50" t="inlineStr">
@@ -25783,7 +25793,7 @@
         </is>
       </c>
       <c r="C402" s="50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D402" s="50" t="inlineStr">
         <is>
@@ -25792,31 +25802,23 @@
       </c>
       <c r="E402" s="53" t="inlineStr">
         <is>
-          <t>李言闻</t>
-        </is>
-      </c>
-      <c r="F402" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F402" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G402" s="51" t="inlineStr"/>
       <c r="H402" s="54" t="inlineStr"/>
-      <c r="I402" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/004/004.png</t>
-        </is>
-      </c>
+      <c r="I402" s="51" t="inlineStr"/>
       <c r="J402" s="53" t="inlineStr">
         <is>
-          <t>今天是上元佳节，咱们全家去城里逛逛，听说今年的灯节格外热闹。</t>
-        </is>
-      </c>
-      <c r="K402" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Music/Story/027/元宵夜樂.mp3</t>
-        </is>
-      </c>
+          <t>太好了，咱们快出发吧。</t>
+        </is>
+      </c>
+      <c r="K402" s="50" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" s="50" t="inlineStr">
@@ -25830,7 +25832,7 @@
         </is>
       </c>
       <c r="C403" s="50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D403" s="50" t="inlineStr">
         <is>
@@ -25839,12 +25841,12 @@
       </c>
       <c r="E403" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
-        </is>
-      </c>
-      <c r="F403" s="51" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F403" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G403" s="51" t="inlineStr"/>
@@ -25852,7 +25854,7 @@
       <c r="I403" s="51" t="inlineStr"/>
       <c r="J403" s="53" t="inlineStr">
         <is>
-          <t>太好了，咱们快出发吧。</t>
+          <t>走。</t>
         </is>
       </c>
       <c r="K403" s="50" t="inlineStr"/>
@@ -25869,29 +25871,33 @@
         </is>
       </c>
       <c r="C404" s="50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D404" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E404" s="53" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F404" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+      <c r="E404" s="50" t="inlineStr">
+        <is>
+          <t>半夏</t>
+        </is>
+      </c>
+      <c r="F404" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G404" s="51" t="inlineStr"/>
-      <c r="H404" s="54" t="inlineStr"/>
-      <c r="I404" s="51" t="inlineStr"/>
+      <c r="H404" s="52" t="inlineStr"/>
+      <c r="I404" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/027/027_01.png</t>
+        </is>
+      </c>
       <c r="J404" s="53" t="inlineStr">
         <is>
-          <t>走。</t>
+          <t>哇，好多人啊！好热闹啊！</t>
         </is>
       </c>
       <c r="K404" s="50" t="inlineStr"/>
@@ -25908,33 +25914,33 @@
         </is>
       </c>
       <c r="C405" s="50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D405" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E405" s="50" t="inlineStr">
-        <is>
-          <t>半夏</t>
-        </is>
-      </c>
-      <c r="F405" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
+      <c r="E405" s="53" t="inlineStr">
+        <is>
+          <t>陈皮</t>
+        </is>
+      </c>
+      <c r="F405" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G405" s="51" t="inlineStr"/>
-      <c r="H405" s="52" t="inlineStr"/>
-      <c r="I405" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/027/027_01.png</t>
-        </is>
-      </c>
+      <c r="H405" s="52" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
+      <c r="I405" s="51" t="inlineStr"/>
       <c r="J405" s="53" t="inlineStr">
         <is>
-          <t>哇，好多人啊！好热闹啊！</t>
+          <t>看你那没见过世面的样子。</t>
         </is>
       </c>
       <c r="K405" s="50" t="inlineStr"/>
@@ -25951,36 +25957,36 @@
         </is>
       </c>
       <c r="C406" s="50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D406" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E406" s="53" t="inlineStr">
-        <is>
-          <t>陈皮</t>
-        </is>
-      </c>
-      <c r="F406" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G406" s="51" t="inlineStr"/>
+      <c r="E406" s="50" t="inlineStr">
+        <is>
+          <t>半夏</t>
+        </is>
+      </c>
+      <c r="F406" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G406" s="55" t="inlineStr"/>
       <c r="H406" s="52" t="inlineStr">
         <is>
           <t>hide</t>
         </is>
       </c>
-      <c r="I406" s="51" t="inlineStr"/>
-      <c r="J406" s="53" t="inlineStr">
-        <is>
-          <t>看你那没见过世面的样子。</t>
-        </is>
-      </c>
-      <c r="K406" s="50" t="inlineStr"/>
+      <c r="I406" s="55" t="inlineStr"/>
+      <c r="J406" s="56" t="inlineStr">
+        <is>
+          <t>找打，你别跑！</t>
+        </is>
+      </c>
+      <c r="K406" s="55" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" s="50" t="inlineStr">
@@ -25994,16 +26000,16 @@
         </is>
       </c>
       <c r="C407" s="50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D407" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E407" s="50" t="inlineStr">
-        <is>
-          <t>半夏</t>
+      <c r="E407" s="53" t="inlineStr">
+        <is>
+          <t>李言闻</t>
         </is>
       </c>
       <c r="F407" s="52" t="inlineStr">
@@ -26012,15 +26018,11 @@
         </is>
       </c>
       <c r="G407" s="55" t="inlineStr"/>
-      <c r="H407" s="52" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
+      <c r="H407" s="55" t="inlineStr"/>
       <c r="I407" s="55" t="inlineStr"/>
       <c r="J407" s="56" t="inlineStr">
         <is>
-          <t>找打，你别跑！</t>
+          <t>那边好像有唱戏的，咱们去那边看看。</t>
         </is>
       </c>
       <c r="K407" s="55" t="inlineStr"/>
@@ -26037,29 +26039,37 @@
         </is>
       </c>
       <c r="C408" s="50" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D408" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E408" s="53" t="inlineStr">
-        <is>
-          <t>李言闻</t>
+      <c r="E408" s="50" t="inlineStr">
+        <is>
+          <t>半夏</t>
         </is>
       </c>
       <c r="F408" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G408" s="55" t="inlineStr"/>
-      <c r="H408" s="55" t="inlineStr"/>
-      <c r="I408" s="55" t="inlineStr"/>
+      <c r="H408" s="52" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
+      <c r="I408" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/027/027_02.png</t>
+        </is>
+      </c>
       <c r="J408" s="56" t="inlineStr">
         <is>
-          <t>那边好像有唱戏的，咱们去那边看看。</t>
+          <t>夫人，那边有座桥，咱们去走百病！</t>
         </is>
       </c>
       <c r="K408" s="55" t="inlineStr"/>
@@ -26076,21 +26086,21 @@
         </is>
       </c>
       <c r="C409" s="50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D409" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E409" s="50" t="inlineStr">
-        <is>
-          <t>半夏</t>
+      <c r="E409" s="53" t="inlineStr">
+        <is>
+          <t>吴芷兰</t>
         </is>
       </c>
       <c r="F409" s="52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G409" s="55" t="inlineStr"/>
@@ -26099,14 +26109,10 @@
           <t>hide</t>
         </is>
       </c>
-      <c r="I409" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/027/027_02.png</t>
-        </is>
-      </c>
+      <c r="I409" s="55" t="inlineStr"/>
       <c r="J409" s="56" t="inlineStr">
         <is>
-          <t>夫人，那边有座桥，咱们去走百病！</t>
+          <t>走，今夜走三桥，一年无灾病。</t>
         </is>
       </c>
       <c r="K409" s="55" t="inlineStr"/>
@@ -26123,7 +26129,7 @@
         </is>
       </c>
       <c r="C410" s="50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D410" s="50" t="inlineStr">
         <is>
@@ -26132,7 +26138,7 @@
       </c>
       <c r="E410" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
+          <t>李言闻</t>
         </is>
       </c>
       <c r="F410" s="52" t="inlineStr">
@@ -26141,15 +26147,11 @@
         </is>
       </c>
       <c r="G410" s="55" t="inlineStr"/>
-      <c r="H410" s="52" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
+      <c r="H410" s="55" t="inlineStr"/>
       <c r="I410" s="55" t="inlineStr"/>
       <c r="J410" s="56" t="inlineStr">
         <is>
-          <t>走，今夜走三桥，一年无灾病。</t>
+          <t>儿子啊，你和芷兰准备啥时候要孩子啊？</t>
         </is>
       </c>
       <c r="K410" s="55" t="inlineStr"/>
@@ -26166,7 +26168,7 @@
         </is>
       </c>
       <c r="C411" s="50" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D411" s="50" t="inlineStr">
         <is>
@@ -26175,12 +26177,12 @@
       </c>
       <c r="E411" s="53" t="inlineStr">
         <is>
-          <t>李言闻</t>
-        </is>
-      </c>
-      <c r="F411" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F411" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G411" s="55" t="inlineStr"/>
@@ -26188,7 +26190,7 @@
       <c r="I411" s="55" t="inlineStr"/>
       <c r="J411" s="56" t="inlineStr">
         <is>
-          <t>儿子啊，你和芷兰准备啥时候要孩子啊？</t>
+          <t>哎哟，爹，您就别操心了。</t>
         </is>
       </c>
       <c r="K411" s="55" t="inlineStr"/>
@@ -26205,7 +26207,7 @@
         </is>
       </c>
       <c r="C412" s="50" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D412" s="50" t="inlineStr">
         <is>
@@ -26214,12 +26216,12 @@
       </c>
       <c r="E412" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F412" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F412" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G412" s="55" t="inlineStr"/>
@@ -26227,7 +26229,7 @@
       <c r="I412" s="55" t="inlineStr"/>
       <c r="J412" s="56" t="inlineStr">
         <is>
-          <t>哎哟，爹，您就别操心了。</t>
+          <t>你们俩一会儿去南门摸摸福气去，听说可灵了。</t>
         </is>
       </c>
       <c r="K412" s="55" t="inlineStr"/>
@@ -26244,7 +26246,7 @@
         </is>
       </c>
       <c r="C413" s="50" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D413" s="50" t="inlineStr">
         <is>
@@ -26253,12 +26255,12 @@
       </c>
       <c r="E413" s="53" t="inlineStr">
         <is>
-          <t>李言闻</t>
-        </is>
-      </c>
-      <c r="F413" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F413" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G413" s="55" t="inlineStr"/>
@@ -26266,7 +26268,7 @@
       <c r="I413" s="55" t="inlineStr"/>
       <c r="J413" s="56" t="inlineStr">
         <is>
-          <t>你们俩一会儿去南门摸摸福气去，听说可灵了。</t>
+          <t>别说了爹，咱们看戏去吧。</t>
         </is>
       </c>
       <c r="K413" s="55" t="inlineStr"/>
@@ -26283,7 +26285,7 @@
         </is>
       </c>
       <c r="C414" s="50" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D414" s="50" t="inlineStr">
         <is>
@@ -26292,20 +26294,20 @@
       </c>
       <c r="E414" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
+          <t>陈皮</t>
         </is>
       </c>
       <c r="F414" s="54" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G414" s="55" t="inlineStr"/>
       <c r="H414" s="55" t="inlineStr"/>
-      <c r="I414" s="55" t="inlineStr"/>
+      <c r="I414" s="51" t="inlineStr"/>
       <c r="J414" s="56" t="inlineStr">
         <is>
-          <t>别说了爹，咱们看戏去吧。</t>
+          <t>老爷，那边儿在唱紫钗记呢。</t>
         </is>
       </c>
       <c r="K414" s="55" t="inlineStr"/>
@@ -26322,29 +26324,25 @@
         </is>
       </c>
       <c r="C415" s="50" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D415" s="50" t="inlineStr">
         <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E415" s="53" t="inlineStr">
-        <is>
-          <t>陈皮</t>
-        </is>
-      </c>
-      <c r="F415" s="54" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E415" s="55" t="inlineStr"/>
+      <c r="F415" s="50" t="inlineStr"/>
       <c r="G415" s="55" t="inlineStr"/>
       <c r="H415" s="55" t="inlineStr"/>
-      <c r="I415" s="51" t="inlineStr"/>
+      <c r="I415" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/027/027_03.png</t>
+        </is>
+      </c>
       <c r="J415" s="56" t="inlineStr">
         <is>
-          <t>老爷，那边儿在唱紫钗记呢。</t>
+          <t>谢皇恩灯华月华，谢天恩春华岁华，遍写着国泰民安天下，遨头去唱声哗。好灯也，说灯花南天门最佳，香车隘挑笼绛纱，喝道转身停马，尘影里看谁家。</t>
         </is>
       </c>
       <c r="K415" s="55" t="inlineStr"/>
@@ -26361,25 +26359,29 @@
         </is>
       </c>
       <c r="C416" s="50" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D416" s="50" t="inlineStr">
         <is>
-          <t>subtitle</t>
-        </is>
-      </c>
-      <c r="E416" s="55" t="inlineStr"/>
-      <c r="F416" s="50" t="inlineStr"/>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E416" s="53" t="inlineStr">
+        <is>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F416" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
       <c r="G416" s="55" t="inlineStr"/>
       <c r="H416" s="55" t="inlineStr"/>
-      <c r="I416" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/027/027_03.png</t>
-        </is>
-      </c>
-      <c r="J416" s="56" t="inlineStr">
-        <is>
-          <t>谢皇恩灯华月华，谢天恩春华岁华，遍写着国泰民安天下，遨头去唱声哗。好灯也，说灯花南天门最佳，香车隘挑笼绛纱，喝道转身停马，尘影里看谁家。</t>
+      <c r="I416" s="55" t="inlineStr"/>
+      <c r="J416" s="55" t="inlineStr">
+        <is>
+          <t>相公，咱们去猜灯谜吧！</t>
         </is>
       </c>
       <c r="K416" s="55" t="inlineStr"/>
@@ -26396,7 +26398,7 @@
         </is>
       </c>
       <c r="C417" s="50" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D417" s="50" t="inlineStr">
         <is>
@@ -26405,12 +26407,12 @@
       </c>
       <c r="E417" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
-        </is>
-      </c>
-      <c r="F417" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F417" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G417" s="55" t="inlineStr"/>
@@ -26418,7 +26420,7 @@
       <c r="I417" s="55" t="inlineStr"/>
       <c r="J417" s="55" t="inlineStr">
         <is>
-          <t>相公，咱们去猜灯谜吧！</t>
+          <t>走！</t>
         </is>
       </c>
       <c r="K417" s="55" t="inlineStr"/>
@@ -26435,7 +26437,7 @@
         </is>
       </c>
       <c r="C418" s="50" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D418" s="50" t="inlineStr">
         <is>
@@ -26454,10 +26456,14 @@
       </c>
       <c r="G418" s="55" t="inlineStr"/>
       <c r="H418" s="55" t="inlineStr"/>
-      <c r="I418" s="55" t="inlineStr"/>
-      <c r="J418" s="55" t="inlineStr">
-        <is>
-          <t>走！</t>
+      <c r="I418" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/027/027_04.png</t>
+        </is>
+      </c>
+      <c r="J418" s="68" t="inlineStr">
+        <is>
+          <t>这么多灯谜，"一点一横长，一撇到南洋，南阳有个人，只有一寸长"，打一个字…</t>
         </is>
       </c>
       <c r="K418" s="55" t="inlineStr"/>
@@ -26474,7 +26480,7 @@
         </is>
       </c>
       <c r="C419" s="50" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D419" s="50" t="inlineStr">
         <is>
@@ -26483,24 +26489,20 @@
       </c>
       <c r="E419" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F419" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F419" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G419" s="55" t="inlineStr"/>
       <c r="H419" s="55" t="inlineStr"/>
-      <c r="I419" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/027/027_04.png</t>
-        </is>
-      </c>
-      <c r="J419" s="68" t="inlineStr">
-        <is>
-          <t>这么多灯谜，"一点一横长，一撇到南洋，南阳有个人，只有一寸长"，打一个字…</t>
+      <c r="I419" s="55" t="inlineStr"/>
+      <c r="J419" s="55" t="inlineStr">
+        <is>
+          <t>我知道，这是个"府"字。</t>
         </is>
       </c>
       <c r="K419" s="55" t="inlineStr"/>
@@ -26517,7 +26519,7 @@
         </is>
       </c>
       <c r="C420" s="50" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D420" s="50" t="inlineStr">
         <is>
@@ -26526,12 +26528,12 @@
       </c>
       <c r="E420" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
-        </is>
-      </c>
-      <c r="F420" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F420" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G420" s="55" t="inlineStr"/>
@@ -26539,7 +26541,7 @@
       <c r="I420" s="55" t="inlineStr"/>
       <c r="J420" s="55" t="inlineStr">
         <is>
-          <t>我知道，这是个"府"字。</t>
+          <t>还是娘子聪慧啊，哈哈。</t>
         </is>
       </c>
       <c r="K420" s="55" t="inlineStr"/>
@@ -26556,7 +26558,7 @@
         </is>
       </c>
       <c r="C421" s="50" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D421" s="50" t="inlineStr">
         <is>
@@ -26565,12 +26567,12 @@
       </c>
       <c r="E421" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F421" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F421" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G421" s="55" t="inlineStr"/>
@@ -26578,7 +26580,7 @@
       <c r="I421" s="55" t="inlineStr"/>
       <c r="J421" s="55" t="inlineStr">
         <is>
-          <t>还是娘子聪慧啊，哈哈。</t>
+          <t>你看这个，"大雪压青松"，打一味药材。</t>
         </is>
       </c>
       <c r="K421" s="55" t="inlineStr"/>
@@ -26595,7 +26597,7 @@
         </is>
       </c>
       <c r="C422" s="50" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D422" s="50" t="inlineStr">
         <is>
@@ -26604,20 +26606,20 @@
       </c>
       <c r="E422" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
-        </is>
-      </c>
-      <c r="F422" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F422" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G422" s="55" t="inlineStr"/>
       <c r="H422" s="55" t="inlineStr"/>
       <c r="I422" s="55" t="inlineStr"/>
-      <c r="J422" s="55" t="inlineStr">
-        <is>
-          <t>你看这个，"大雪压青松"，打一味药材。</t>
+      <c r="J422" s="68" t="inlineStr">
+        <is>
+          <t>这个我会，是"忍冬"。</t>
         </is>
       </c>
       <c r="K422" s="55" t="inlineStr"/>
@@ -26634,7 +26636,7 @@
         </is>
       </c>
       <c r="C423" s="50" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D423" s="50" t="inlineStr">
         <is>
@@ -26643,12 +26645,12 @@
       </c>
       <c r="E423" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F423" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F423" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G423" s="55" t="inlineStr"/>
@@ -26656,7 +26658,7 @@
       <c r="I423" s="55" t="inlineStr"/>
       <c r="J423" s="68" t="inlineStr">
         <is>
-          <t>这个我会，是"忍冬"。</t>
+          <t>东璧，芷兰，咱们去小摊儿坐会儿吃点元宵。</t>
         </is>
       </c>
       <c r="K423" s="55" t="inlineStr"/>
@@ -26673,7 +26675,7 @@
         </is>
       </c>
       <c r="C424" s="50" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D424" s="50" t="inlineStr">
         <is>
@@ -26692,10 +26694,14 @@
       </c>
       <c r="G424" s="55" t="inlineStr"/>
       <c r="H424" s="55" t="inlineStr"/>
-      <c r="I424" s="55" t="inlineStr"/>
-      <c r="J424" s="68" t="inlineStr">
-        <is>
-          <t>东璧，芷兰，咱们去小摊儿坐会儿吃点元宵。</t>
+      <c r="I424" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/027/027_05.png</t>
+        </is>
+      </c>
+      <c r="J424" s="55" t="inlineStr">
+        <is>
+          <t>干了一年坐堂医，感觉怎么样，和你之前想的一样吗？</t>
         </is>
       </c>
       <c r="K424" s="55" t="inlineStr"/>
@@ -26712,7 +26718,7 @@
         </is>
       </c>
       <c r="C425" s="50" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D425" s="50" t="inlineStr">
         <is>
@@ -26721,24 +26727,20 @@
       </c>
       <c r="E425" s="53" t="inlineStr">
         <is>
-          <t>李言闻</t>
-        </is>
-      </c>
-      <c r="F425" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F425" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G425" s="55" t="inlineStr"/>
       <c r="H425" s="55" t="inlineStr"/>
-      <c r="I425" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/027/027_05.png</t>
-        </is>
-      </c>
+      <c r="I425" s="55" t="inlineStr"/>
       <c r="J425" s="55" t="inlineStr">
         <is>
-          <t>干了一年坐堂医，感觉怎么样，和你之前想的一样吗？</t>
+          <t>我倒是挺喜欢这一行，只是赚不到什么钱，苦了您和芷兰了…</t>
         </is>
       </c>
       <c r="K425" s="55" t="inlineStr"/>
@@ -26755,7 +26757,7 @@
         </is>
       </c>
       <c r="C426" s="50" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D426" s="50" t="inlineStr">
         <is>
@@ -26764,12 +26766,12 @@
       </c>
       <c r="E426" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F426" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F426" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G426" s="55" t="inlineStr"/>
@@ -26777,7 +26779,7 @@
       <c r="I426" s="55" t="inlineStr"/>
       <c r="J426" s="55" t="inlineStr">
         <is>
-          <t>我倒是挺喜欢这一行，只是赚不到什么钱，苦了您和芷兰了…</t>
+          <t>只要咱们一家人能一起平平安安的过日子，我就知足了，要那么多钱做什么。</t>
         </is>
       </c>
       <c r="K426" s="55" t="inlineStr"/>
@@ -26794,7 +26796,7 @@
         </is>
       </c>
       <c r="C427" s="50" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D427" s="50" t="inlineStr">
         <is>
@@ -26803,12 +26805,12 @@
       </c>
       <c r="E427" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
+          <t>李言闻</t>
         </is>
       </c>
       <c r="F427" s="52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G427" s="55" t="inlineStr"/>
@@ -26816,7 +26818,7 @@
       <c r="I427" s="55" t="inlineStr"/>
       <c r="J427" s="55" t="inlineStr">
         <is>
-          <t>只要咱们一家人能一起平平安安的过日子，我就知足了，要那么多钱做什么。</t>
+          <t>是啊，一家人平平安安就好啊。</t>
         </is>
       </c>
       <c r="K427" s="55" t="inlineStr"/>
@@ -26833,7 +26835,7 @@
         </is>
       </c>
       <c r="C428" s="50" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D428" s="50" t="inlineStr">
         <is>
@@ -26855,49 +26857,23 @@
       <c r="I428" s="55" t="inlineStr"/>
       <c r="J428" s="55" t="inlineStr">
         <is>
-          <t>是啊，一家人平平安安就好啊。</t>
+          <t>好了，不早了，咱们该回家了。</t>
         </is>
       </c>
       <c r="K428" s="55" t="inlineStr"/>
     </row>
     <row r="429">
-      <c r="A429" s="50" t="inlineStr">
-        <is>
-          <t>027</t>
-        </is>
-      </c>
-      <c r="B429" s="50" t="inlineStr">
-        <is>
-          <t>上元灯节</t>
-        </is>
-      </c>
-      <c r="C429" s="50" t="n">
-        <v>28</v>
-      </c>
-      <c r="D429" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E429" s="53" t="inlineStr">
-        <is>
-          <t>李言闻</t>
-        </is>
-      </c>
-      <c r="F429" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G429" s="55" t="inlineStr"/>
-      <c r="H429" s="55" t="inlineStr"/>
-      <c r="I429" s="55" t="inlineStr"/>
-      <c r="J429" s="55" t="inlineStr">
-        <is>
-          <t>好了，不早了，咱们该回家了。</t>
-        </is>
-      </c>
-      <c r="K429" s="55" t="inlineStr"/>
+      <c r="A429" s="50" t="n"/>
+      <c r="B429" s="50" t="n"/>
+      <c r="C429" s="50" t="n"/>
+      <c r="D429" s="50" t="n"/>
+      <c r="E429" s="53" t="n"/>
+      <c r="F429" s="52" t="n"/>
+      <c r="G429" s="55" t="n"/>
+      <c r="H429" s="55" t="n"/>
+      <c r="I429" s="55" t="n"/>
+      <c r="J429" s="55" t="n"/>
+      <c r="K429" s="55" t="n"/>
     </row>
     <row r="430">
       <c r="A430" s="50" t="n"/>
@@ -29137,8 +29113,8 @@
     <col width="5.125" customWidth="1" style="35" min="27" max="27"/>
     <col width="5" customWidth="1" style="35" min="28" max="28"/>
     <col width="5.25" customWidth="1" style="35" min="29" max="29"/>
-    <col width="9" customWidth="1" style="9" min="30" max="133"/>
-    <col width="9" customWidth="1" style="9" min="134" max="16384"/>
+    <col width="9" customWidth="1" style="9" min="30" max="134"/>
+    <col width="9" customWidth="1" style="9" min="135" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -52160,8 +52136,8 @@
     <cfRule type="duplicateValues" priority="2366" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A77 A79:A100 A102:A106 A114:A1048576">
+    <cfRule type="duplicateValues" priority="2332" dxfId="0"/>
     <cfRule type="duplicateValues" priority="2331" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="2332" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A5">
     <cfRule type="duplicateValues" priority="162" dxfId="0"/>
@@ -52188,32 +52164,32 @@
     <cfRule type="duplicateValues" priority="126" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" priority="124" dxfId="0"/>
     <cfRule type="duplicateValues" priority="123" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="124" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
     <cfRule type="duplicateValues" priority="121" dxfId="0"/>
     <cfRule type="duplicateValues" priority="122" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17">
+    <cfRule type="duplicateValues" priority="120" dxfId="0"/>
     <cfRule type="duplicateValues" priority="119" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="120" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18">
+    <cfRule type="duplicateValues" priority="118" dxfId="0"/>
     <cfRule type="duplicateValues" priority="117" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="118" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:A20">
+    <cfRule type="duplicateValues" priority="116" dxfId="0"/>
     <cfRule type="duplicateValues" priority="115" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="116" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
     <cfRule type="duplicateValues" priority="112" dxfId="0"/>
     <cfRule type="duplicateValues" priority="113" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A26">
+    <cfRule type="duplicateValues" priority="111" dxfId="0"/>
     <cfRule type="duplicateValues" priority="110" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="111" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27">
     <cfRule type="duplicateValues" priority="140" dxfId="0"/>
@@ -52252,20 +52228,20 @@
     <cfRule type="duplicateValues" priority="632" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40">
+    <cfRule type="duplicateValues" priority="155" dxfId="0"/>
     <cfRule type="duplicateValues" priority="154" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="155" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41">
     <cfRule type="duplicateValues" priority="78" dxfId="0"/>
     <cfRule type="duplicateValues" priority="79" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43">
+    <cfRule type="duplicateValues" priority="77" dxfId="0"/>
     <cfRule type="duplicateValues" priority="76" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="77" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44">
+    <cfRule type="duplicateValues" priority="147" dxfId="0"/>
     <cfRule type="duplicateValues" priority="146" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="147" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45">
     <cfRule type="duplicateValues" priority="90" dxfId="0"/>
@@ -52276,8 +52252,8 @@
     <cfRule type="duplicateValues" priority="94" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:A48">
+    <cfRule type="duplicateValues" priority="55" dxfId="0"/>
     <cfRule type="duplicateValues" priority="54" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="55" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:A52">
     <cfRule type="duplicateValues" priority="106" dxfId="0"/>
@@ -52288,32 +52264,32 @@
     <cfRule type="duplicateValues" priority="45" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54">
+    <cfRule type="duplicateValues" priority="29" dxfId="0"/>
     <cfRule type="duplicateValues" priority="28" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="29" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55">
+    <cfRule type="duplicateValues" priority="134" dxfId="0"/>
     <cfRule type="duplicateValues" priority="133" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="134" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56">
+    <cfRule type="duplicateValues" priority="50" dxfId="0"/>
     <cfRule type="duplicateValues" priority="49" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="50" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57">
+    <cfRule type="duplicateValues" priority="149" dxfId="0"/>
     <cfRule type="duplicateValues" priority="148" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="149" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58">
     <cfRule type="duplicateValues" priority="152" dxfId="0"/>
     <cfRule type="duplicateValues" priority="153" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59">
+    <cfRule type="duplicateValues" priority="74" dxfId="0"/>
     <cfRule type="duplicateValues" priority="73" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="74" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A60">
+    <cfRule type="duplicateValues" priority="72" dxfId="0"/>
     <cfRule type="duplicateValues" priority="71" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="72" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61">
     <cfRule type="duplicateValues" priority="86" dxfId="0"/>
@@ -52324,8 +52300,8 @@
     <cfRule type="duplicateValues" priority="70" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63">
+    <cfRule type="duplicateValues" priority="66" dxfId="0"/>
     <cfRule type="duplicateValues" priority="65" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="66" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64">
     <cfRule type="duplicateValues" priority="60" dxfId="0"/>
@@ -52336,8 +52312,8 @@
     <cfRule type="duplicateValues" priority="59" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A66">
+    <cfRule type="duplicateValues" priority="57" dxfId="0"/>
     <cfRule type="duplicateValues" priority="56" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="57" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A67">
     <cfRule type="duplicateValues" priority="150" dxfId="0"/>
@@ -52348,8 +52324,8 @@
     <cfRule type="duplicateValues" priority="866" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69">
+    <cfRule type="duplicateValues" priority="53" dxfId="0"/>
     <cfRule type="duplicateValues" priority="52" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="53" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70">
     <cfRule type="duplicateValues" priority="42" dxfId="0"/>
@@ -52360,36 +52336,36 @@
     <cfRule type="duplicateValues" priority="10" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A72:A73">
+    <cfRule type="duplicateValues" priority="100" dxfId="0"/>
     <cfRule type="duplicateValues" priority="99" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="100" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A74">
     <cfRule type="duplicateValues" priority="95" dxfId="0"/>
     <cfRule type="duplicateValues" priority="96" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A75:A77">
+    <cfRule type="duplicateValues" priority="39" dxfId="0"/>
     <cfRule type="duplicateValues" priority="38" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="39" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A78">
+    <cfRule type="duplicateValues" priority="2" dxfId="0"/>
     <cfRule type="duplicateValues" priority="1" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="2" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A79 A106">
     <cfRule type="duplicateValues" priority="1727" dxfId="0"/>
     <cfRule type="duplicateValues" priority="1728" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A80">
+    <cfRule type="duplicateValues" priority="63" dxfId="0"/>
     <cfRule type="duplicateValues" priority="62" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="63" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A82:A83">
     <cfRule type="duplicateValues" priority="982" dxfId="0"/>
     <cfRule type="duplicateValues" priority="983" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A84">
+    <cfRule type="duplicateValues" priority="136" dxfId="0"/>
     <cfRule type="duplicateValues" priority="135" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="136" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A85">
     <cfRule type="duplicateValues" priority="13" dxfId="0"/>
@@ -52420,12 +52396,12 @@
     <cfRule type="duplicateValues" priority="41" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A96">
+    <cfRule type="duplicateValues" priority="85" dxfId="0"/>
     <cfRule type="duplicateValues" priority="84" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="85" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A98">
+    <cfRule type="duplicateValues" priority="17" dxfId="0"/>
     <cfRule type="duplicateValues" priority="16" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="17" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A99">
     <cfRule type="duplicateValues" priority="26" dxfId="0"/>
@@ -52440,12 +52416,12 @@
     <cfRule type="duplicateValues" priority="4" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A102">
+    <cfRule type="duplicateValues" priority="89" dxfId="0"/>
     <cfRule type="duplicateValues" priority="88" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="89" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A103">
+    <cfRule type="duplicateValues" priority="143" dxfId="0"/>
     <cfRule type="duplicateValues" priority="142" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="143" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A104:A105">
     <cfRule type="duplicateValues" priority="1709" dxfId="0"/>
@@ -52456,8 +52432,8 @@
     <cfRule type="duplicateValues" priority="1944" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A114:A115">
+    <cfRule type="duplicateValues" priority="132" dxfId="0"/>
     <cfRule type="duplicateValues" priority="131" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="132" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A117:A1048576">
     <cfRule type="duplicateValues" priority="395" dxfId="0"/>

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -301,7 +301,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -508,6 +508,9 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -10032,7 +10035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K442"/>
+  <dimension ref="A1:K448"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="18"/>
   <cols>
     <col width="8.75" customWidth="1" style="10" min="1" max="1"/>
@@ -27076,7 +27079,7 @@
       </c>
       <c r="K428" s="55" t="inlineStr"/>
     </row>
-    <row r="429">
+    <row r="429" ht="30" customHeight="1">
       <c r="A429" s="50" t="inlineStr">
         <is>
           <t>028_01</t>
@@ -27114,7 +27117,7 @@
       </c>
       <c r="J429" s="53" t="inlineStr">
         <is>
-          <t>大夫啊，您快帮忙看看吧，这孩子整日目光呆滞，叫他也不应，就在那自言自语考中了考中了的…</t>
+          <t>大夫啊，您快给看看吧，这孩子整日目光呆滞，叫他也不应，就在那自言自语，嘴里不知道嘟囔这什么，怪邪乎的…</t>
         </is>
       </c>
       <c r="K429" s="50" t="inlineStr"/>
@@ -27262,7 +27265,7 @@
       </c>
       <c r="J433" s="53" t="inlineStr">
         <is>
-          <t>贵公子所患的是痰迷心窍之症，开副涤痰汤调理一下。</t>
+          <t>公子所患的是痰迷心窍之症，开副涤痰汤调理一下。</t>
         </is>
       </c>
       <c r="K433" s="50" t="inlineStr"/>
@@ -27533,9 +27536,9 @@
       <c r="G440" s="55" t="inlineStr"/>
       <c r="H440" s="55" t="inlineStr"/>
       <c r="I440" s="55" t="inlineStr"/>
-      <c r="J440" s="56" t="inlineStr">
-        <is>
-          <t>很多人表面看着正常，其实病得都不轻呢。</t>
+      <c r="J440" s="53" t="inlineStr">
+        <is>
+          <t>很多人表面上看着正常，其实都病得不轻呢。</t>
         </is>
       </c>
       <c r="K440" s="55" t="inlineStr"/>
@@ -27572,9 +27575,9 @@
       <c r="G441" s="55" t="inlineStr"/>
       <c r="H441" s="55" t="inlineStr"/>
       <c r="I441" s="55" t="inlineStr"/>
-      <c r="J441" s="56" t="inlineStr">
-        <is>
-          <t>胡扯，我看你就是没病说成有病，</t>
+      <c r="J441" s="53" t="inlineStr">
+        <is>
+          <t>胡扯，我看你就是没病说成有病，骗病人买药赚钱</t>
         </is>
       </c>
       <c r="K441" s="55" t="inlineStr"/>
@@ -27582,45 +27585,279 @@
     <row r="442">
       <c r="A442" s="50" t="inlineStr">
         <is>
+          <t>028_02</t>
+        </is>
+      </c>
+      <c r="B442" s="50" t="inlineStr">
+        <is>
+          <t>028治疗成功</t>
+        </is>
+      </c>
+      <c r="C442" s="50" t="n">
+        <v>10</v>
+      </c>
+      <c r="D442" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E442" s="53" t="inlineStr">
+        <is>
+          <t>曾和</t>
+        </is>
+      </c>
+      <c r="F442" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G442" s="55" t="inlineStr"/>
+      <c r="H442" s="55" t="inlineStr"/>
+      <c r="I442" s="55" t="inlineStr"/>
+      <c r="J442" s="53" t="inlineStr">
+        <is>
+          <t>咱们家可是花了好多钱，把地都卖了供你读书，就只望着你能出人头地，光宗耀祖。可你怎么就这么不争气呢？</t>
+        </is>
+      </c>
+      <c r="K442" s="55" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" s="50" t="inlineStr">
+        <is>
+          <t>028_02</t>
+        </is>
+      </c>
+      <c r="B443" s="50" t="inlineStr">
+        <is>
+          <t>028治疗成功</t>
+        </is>
+      </c>
+      <c r="C443" s="50" t="n">
+        <v>11</v>
+      </c>
+      <c r="D443" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E443" s="53" t="inlineStr">
+        <is>
+          <t>曾题名</t>
+        </is>
+      </c>
+      <c r="F443" s="54" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G443" s="55" t="inlineStr"/>
+      <c r="H443" s="55" t="inlineStr"/>
+      <c r="I443" s="55" t="inlineStr"/>
+      <c r="J443" s="53" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="K443" s="55" t="inlineStr"/>
+    </row>
+    <row r="444">
+      <c r="A444" s="50" t="inlineStr">
+        <is>
+          <t>028_02</t>
+        </is>
+      </c>
+      <c r="B444" s="50" t="inlineStr">
+        <is>
+          <t>028治疗成功</t>
+        </is>
+      </c>
+      <c r="C444" s="50" t="n">
+        <v>12</v>
+      </c>
+      <c r="D444" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E444" s="53" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F444" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G444" s="55" t="inlineStr"/>
+      <c r="H444" s="55" t="inlineStr"/>
+      <c r="I444" s="55" t="inlineStr"/>
+      <c r="J444" s="88" t="inlineStr">
+        <is>
+          <t>这位仁兄，我也是读过书考过科举的，读书人其实也是有很多难处的。</t>
+        </is>
+      </c>
+      <c r="K444" s="55" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" s="50" t="inlineStr">
+        <is>
+          <t>028_02</t>
+        </is>
+      </c>
+      <c r="B445" s="50" t="inlineStr">
+        <is>
+          <t>028治疗成功</t>
+        </is>
+      </c>
+      <c r="C445" s="50" t="n">
+        <v>13</v>
+      </c>
+      <c r="D445" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E445" s="53" t="inlineStr">
+        <is>
+          <t>曾和</t>
+        </is>
+      </c>
+      <c r="F445" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G445" s="55" t="inlineStr"/>
+      <c r="H445" s="55" t="inlineStr"/>
+      <c r="I445" s="55" t="inlineStr"/>
+      <c r="J445" s="88" t="inlineStr">
+        <is>
+          <t>难？还能有我赚钱养家糊口难？天底下还能有比我们做父母更难的？</t>
+        </is>
+      </c>
+      <c r="K445" s="55" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" s="50" t="inlineStr">
+        <is>
+          <t>028_02</t>
+        </is>
+      </c>
+      <c r="B446" s="50" t="inlineStr">
+        <is>
+          <t>028治疗成功</t>
+        </is>
+      </c>
+      <c r="C446" s="50" t="n">
+        <v>14</v>
+      </c>
+      <c r="D446" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E446" s="53" t="inlineStr">
+        <is>
+          <t>曾和</t>
+        </is>
+      </c>
+      <c r="F446" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G446" s="55" t="inlineStr"/>
+      <c r="H446" s="55" t="inlineStr"/>
+      <c r="I446" s="55" t="inlineStr"/>
+      <c r="J446" s="88" t="inlineStr">
+        <is>
+          <t>再过半年可就要考试了，你这次无论如何也要给我好好考。</t>
+        </is>
+      </c>
+      <c r="K446" s="55" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" s="50" t="inlineStr">
+        <is>
+          <t>028_02</t>
+        </is>
+      </c>
+      <c r="B447" s="50" t="inlineStr">
+        <is>
+          <t>028治疗成功</t>
+        </is>
+      </c>
+      <c r="C447" s="50" t="n">
+        <v>15</v>
+      </c>
+      <c r="D447" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E447" s="53" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F447" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G447" s="55" t="inlineStr"/>
+      <c r="H447" s="55" t="inlineStr"/>
+      <c r="I447" s="55" t="inlineStr"/>
+      <c r="J447" s="88" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K447" s="55" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" s="50" t="inlineStr">
+        <is>
           <t>028_03</t>
         </is>
       </c>
-      <c r="B442" s="50" t="inlineStr">
+      <c r="B448" s="50" t="inlineStr">
         <is>
           <t>028治疗失败</t>
         </is>
       </c>
-      <c r="C442" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D442" s="50" t="inlineStr">
+      <c r="C448" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D448" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E442" s="53" t="inlineStr">
+      <c r="E448" s="53" t="inlineStr">
         <is>
           <t>李东璧</t>
         </is>
       </c>
-      <c r="F442" s="52" t="inlineStr">
+      <c r="F448" s="52" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="G442" s="51" t="inlineStr"/>
-      <c r="H442" s="54" t="inlineStr"/>
-      <c r="I442" s="51" t="inlineStr">
+      <c r="G448" s="51" t="inlineStr"/>
+      <c r="H448" s="54" t="inlineStr"/>
+      <c r="I448" s="51" t="inlineStr">
         <is>
           <t>current_scene</t>
         </is>
       </c>
-      <c r="J442" s="53" t="inlineStr">
+      <c r="J448" s="53" t="inlineStr">
         <is>
           <t>不对，我需要好好想想这是什么病，该开什么方。</t>
         </is>
       </c>
-      <c r="K442" s="50" t="inlineStr"/>
+      <c r="K448" s="50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -7242,7 +7242,7 @@
         </is>
       </c>
       <c r="H8" s="48" t="n">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="I8" s="48" t="inlineStr"/>
       <c r="J8" s="48" t="inlineStr"/>

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -32023,7 +32023,7 @@
 【主治】痰迷心窍
 【组成】
 君：半夏 二钱五分，胆南星 二钱五分
-臣：枳实 二钱，陈皮 一分五钱
+臣：枳实 二钱，陈皮 一钱五分
 佐：竹茹 一钱，茯苓 二钱，石菖蒲 一钱，人参 一钱
 使：生姜 一钱，甘草 一钱
 【配伍】

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -32615,7 +32615,7 @@
 君：钩藤 三钱，菊花 三钱
 臣：防风 三钱，石膏 三钱
 佐：茯苓 三钱，半夏 三钱，陈皮 三钱，人参 三钱
-使：甘草 三钱
+使：甘草 三钱，生姜 二钱
 【配伍】
 钩藤、菊花：平肝息风、清利头目
 石膏：清热泻火、除烦止晕

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -6954,15 +6954,13 @@
       </c>
       <c r="E2" s="48" t="inlineStr"/>
       <c r="F2" s="48" t="inlineStr"/>
-      <c r="G2" s="48" t="inlineStr">
-        <is>
-          <t>gte</t>
-        </is>
-      </c>
-      <c r="H2" s="48" t="n">
-        <v>107</v>
-      </c>
-      <c r="I2" s="48" t="inlineStr"/>
+      <c r="G2" s="48" t="inlineStr"/>
+      <c r="H2" s="48" t="inlineStr"/>
+      <c r="I2" s="48" t="inlineStr">
+        <is>
+          <t>气分热盛</t>
+        </is>
+      </c>
       <c r="J2" s="48" t="inlineStr">
         <is>
           <t>021</t>
@@ -7048,7 +7046,7 @@
         </is>
       </c>
       <c r="D4" s="48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="48" t="inlineStr"/>
       <c r="F4" s="48" t="inlineStr"/>
@@ -7093,7 +7091,9 @@
           <t>night</t>
         </is>
       </c>
-      <c r="D5" s="48" t="inlineStr"/>
+      <c r="D5" s="48" t="n">
+        <v>1</v>
+      </c>
       <c r="E5" s="48" t="inlineStr"/>
       <c r="F5" s="48" t="inlineStr"/>
       <c r="G5" s="48" t="inlineStr"/>
@@ -8170,7 +8170,7 @@
       <c r="H27" s="48" t="inlineStr"/>
       <c r="I27" s="48" t="inlineStr">
         <is>
-          <t>鸡子黄</t>
+          <t>气分热盛</t>
         </is>
       </c>
       <c r="J27" s="48" t="inlineStr">
@@ -10110,7 +10110,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="33" customHeight="1">
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="50" t="inlineStr">
         <is>
           <t>000_01</t>
@@ -11359,7 +11359,7 @@
       </c>
       <c r="K32" s="50" t="inlineStr"/>
     </row>
-    <row r="33" ht="33" customHeight="1">
+    <row r="33" ht="30" customHeight="1">
       <c r="A33" s="50" t="inlineStr">
         <is>
           <t>000_04</t>
@@ -16512,7 +16512,7 @@
       </c>
       <c r="K163" s="50" t="inlineStr"/>
     </row>
-    <row r="164">
+    <row r="164" ht="33" customHeight="1">
       <c r="A164" s="50" t="inlineStr">
         <is>
           <t>009</t>
@@ -32661,7 +32661,7 @@
 君：柴胡 三钱
 臣：当归 三钱，白芍 三钱
 佐：白术 三钱，茯苓 三钱，生姜 一钱，薄荷 一钱
-使：甘草 一钱五分
+使：甘草 一钱
 【配伍】
 柴胡：疏肝解郁、条达肝气，疏散郁滞。
 当归、白芍：养血柔肝，补肝体、缓肝急；防肝郁化火伤阴。

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -31623,7 +31623,7 @@
           <t>大青龙汤
 【出处】《伤寒论》
 【功效】发汗解表，兼清里热
-【主治】外寒里热
+【主治】表寒里热
 【组成】
 君：麻黄 六钱
 臣：桂枝 二钱，石膏 一两

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -7158,7 +7158,7 @@
         </is>
       </c>
       <c r="F6" s="48" t="n">
-        <v>1000</v>
+        <v>1000000</v>
       </c>
       <c r="G6" s="48" t="inlineStr"/>
       <c r="H6" s="48" t="inlineStr"/>

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -10132,7 +10132,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="33" customHeight="1">
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="50" t="inlineStr">
         <is>
           <t>000_01</t>
@@ -10157,7 +10157,7 @@
       <c r="H2" s="52" t="inlineStr"/>
       <c r="I2" s="51" t="inlineStr">
         <is>
-          <t>current_scene</t>
+          <t>res://Assets/Background/black.png</t>
         </is>
       </c>
       <c r="J2" s="53" t="inlineStr">

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="600" firstSheet="0" activeTab="9" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="600" firstSheet="0" activeTab="9" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" state="visible" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Story'!$A$1:$AA$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'StoryLine'!$A$1:$BI$453</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -178,10 +178,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="BIZ UDGothic"/>
-      <charset val="128"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <family val="3"/>
-      <sz val="6"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="游ゴシック"/>
@@ -521,7 +521,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="162">
     <dxf>
@@ -2428,8 +2428,8 @@
     <col width="25.5" bestFit="1" customWidth="1" style="23" min="7" max="7"/>
     <col width="31.75" bestFit="1" customWidth="1" style="23" min="8" max="8"/>
     <col width="33.875" bestFit="1" customWidth="1" style="23" min="9" max="9"/>
-    <col width="9.125" customWidth="1" style="23" min="10" max="92"/>
-    <col width="9.125" customWidth="1" style="23" min="93" max="16384"/>
+    <col width="9.125" customWidth="1" style="23" min="10" max="93"/>
+    <col width="9.125" customWidth="1" style="23" min="94" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.4" customHeight="1">
@@ -5631,7 +5631,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F47"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.65"/>
   <cols>
     <col width="21.75" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
@@ -5888,7 +5888,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -6809,6 +6809,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -6835,8 +6836,8 @@
     <col width="8.375" bestFit="1" customWidth="1" style="46" min="16" max="18"/>
     <col width="10.75" customWidth="1" style="46" min="19" max="19"/>
     <col width="10" bestFit="1" customWidth="1" style="46" min="20" max="20"/>
-    <col width="9" customWidth="1" style="47" min="21" max="42"/>
-    <col width="9" customWidth="1" style="47" min="43" max="16384"/>
+    <col width="9" customWidth="1" style="47" min="21" max="43"/>
+    <col width="9" customWidth="1" style="47" min="44" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customFormat="1" customHeight="1" s="46">
@@ -10071,8 +10072,8 @@
     <col width="48" customWidth="1" style="10" min="9" max="9"/>
     <col width="150.5" customWidth="1" style="64" min="10" max="10"/>
     <col width="8.875" customWidth="1" style="66" min="11" max="11"/>
-    <col width="8.875" customWidth="1" style="36" min="12" max="66"/>
-    <col width="8.875" customWidth="1" style="36" min="67" max="16384"/>
+    <col width="8.875" customWidth="1" style="36" min="12" max="67"/>
+    <col width="8.875" customWidth="1" style="36" min="68" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23415,11 +23416,7 @@
       <c r="F338" s="51" t="inlineStr"/>
       <c r="G338" s="55" t="inlineStr"/>
       <c r="H338" s="55" t="inlineStr"/>
-      <c r="I338" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/black.png</t>
-        </is>
-      </c>
+      <c r="I338" s="51" t="inlineStr"/>
       <c r="J338" s="86" t="inlineStr">
         <is>
           <t>收入一两白银</t>
@@ -23458,11 +23455,7 @@
       </c>
       <c r="G339" s="55" t="inlineStr"/>
       <c r="H339" s="55" t="inlineStr"/>
-      <c r="I339" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
+      <c r="I339" s="51" t="inlineStr"/>
       <c r="J339" s="68" t="inlineStr">
         <is>
           <t>大夫，刚才那姑娘是得了什么病啊？</t>
@@ -24539,11 +24532,7 @@
       <c r="F366" s="52" t="inlineStr"/>
       <c r="G366" s="55" t="inlineStr"/>
       <c r="H366" s="55" t="inlineStr"/>
-      <c r="I366" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/black.png</t>
-        </is>
-      </c>
+      <c r="I366" s="51" t="inlineStr"/>
       <c r="J366" s="56" t="inlineStr">
         <is>
           <t>收入一两白银</t>
@@ -24574,11 +24563,7 @@
       <c r="F367" s="51" t="inlineStr"/>
       <c r="G367" s="55" t="inlineStr"/>
       <c r="H367" s="55" t="inlineStr"/>
-      <c r="I367" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
+      <c r="I367" s="51" t="inlineStr"/>
       <c r="J367" s="56" t="inlineStr">
         <is>
           <t>次日</t>
@@ -28050,7 +28035,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G114"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="37" customWidth="1" style="3" min="1" max="1"/>
     <col width="19.25" customWidth="1" style="3" min="2" max="2"/>
@@ -30238,7 +30223,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AC50"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col width="19" customWidth="1" style="4" min="1" max="1"/>
     <col width="4.5" customWidth="1" style="32" min="2" max="2"/>
@@ -30263,8 +30248,8 @@
     <col width="5.125" customWidth="1" style="35" min="27" max="27"/>
     <col width="5" customWidth="1" style="35" min="28" max="28"/>
     <col width="5.25" customWidth="1" style="35" min="29" max="29"/>
-    <col width="9" customWidth="1" style="9" min="30" max="140"/>
-    <col width="9" customWidth="1" style="9" min="141" max="16384"/>
+    <col width="9" customWidth="1" style="9" min="30" max="141"/>
+    <col width="9" customWidth="1" style="9" min="142" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -31074,7 +31059,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.65"/>
   <cols>
     <col width="25.5" customWidth="1" style="3" min="1" max="1"/>
     <col width="15.125" customWidth="1" style="3" min="2" max="2"/>
@@ -33328,7 +33313,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G357"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="14.375" customWidth="1" style="4" min="1" max="1"/>
     <col width="11.875" customWidth="1" style="4" min="2" max="2"/>
@@ -45107,7 +45092,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M129"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="16.25" customWidth="1" style="7" min="1" max="1"/>
     <col width="11.625" customWidth="1" style="7" min="2" max="2"/>
@@ -53599,7 +53584,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.65"/>
   <cols>
     <col width="45.625" customWidth="1" min="1" max="1"/>
     <col width="23.5" customWidth="1" min="2" max="2"/>

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -28118,7 +28118,7 @@
 【病机】寒邪束表、腠理闭塞、卫阳被遏。
 【症状】恶寒发热，头身酸疼，无汗而喘。
 【脉象】
-浮脉（表）：波峰高，波速慢
+浮脉（表）：波峰高，脉搏次数少
 【标准方】麻黄汤</t>
         </is>
       </c>
@@ -28158,7 +28158,7 @@
 【病机】风寒袭表，卫气不固，营阴外泄。
 【症状】恶风发热，头痛流清涕，出汗。
 【脉象】
-浮脉（表）：波峰低，波速慢
+浮脉（表）：波峰低，脉搏次数少
 【标准方】桂枝汤</t>
         </is>
       </c>
@@ -28198,7 +28198,7 @@
 【病机】风热之邪侵袭肺卫，卫气失和，肺失清肃。
 【症状】发热重，咽喉红肿，痰涕黄稠。
 【脉象】
-浮脉（表）：波速快
+浮脉（表）：脉搏次数多
 【标准方】银翘散</t>
         </is>
       </c>
@@ -28238,7 +28238,7 @@
 【病机】初秋燥热之邪侵袭肺卫，肺失清润。
 【症状】发热恶风，口鼻干燥、咽干口渴、干咳少痰，痰涕黄稠。
 【脉象】
-浮脉（表）：波速快，波宽窄
+浮脉（表）：脉搏次数多，波宽窄
 【标准方】桑杏汤</t>
         </is>
       </c>
@@ -28278,7 +28278,7 @@
 【病机】深秋寒气渐生，燥邪兼风寒侵袭肺卫。
 【症状】恶寒发热、鼻塞流清涕、干咳少痰、咽干唇燥、皮肤干燥。
 【脉象】
-浮脉（表）：波速慢，波宽窄
+浮脉（表）：脉搏次数少，波宽窄
 【标准方】杏苏散</t>
         </is>
       </c>
@@ -28358,7 +28358,7 @@
 【病机】风寒湿邪痹阻经络，寒邪偏盛。寒主收引、凝滞，气血不通则疼痛剧烈。
 【症状】肢体关节疼痛剧烈、固定不移；遇寒加重、得温痛减；关节屈伸不利，局部怕冷。
 【脉象】
-浮脉（表）：波峰高（轻微），波速慢（剧烈），波宽宽（轻微）
+浮脉（表）：波峰高（轻微），脉搏次数少（剧烈），波宽宽（轻微）
 【标准方】乌头汤</t>
         </is>
       </c>
@@ -28398,7 +28398,7 @@
 【病机】风湿热邪侵袭经络关节，或风寒湿邪郁而化热，气血壅滞、经络痹阻。
 【症状】关节红肿灼热、疼痛剧烈；触之发热、拒按，得冷稍舒；发热、口渴、烦躁；肢体屈伸不利。
 【脉象】
-浮脉（表）：波峰高（轻微），波速快（剧烈），波宽宽（轻微）
+浮脉（表）：波峰高（轻微），脉搏次数多（剧烈），波宽宽（轻微）
 【标准方】白虎桂枝汤</t>
         </is>
       </c>
@@ -28439,7 +28439,7 @@
 【症状】关节沉重酸痛、重着如裹；痛处固定，肌肤麻木、肢体困重；关节肿胀、屈伸不利。
 阴雨潮湿天气加重
 【脉象】
-浮脉（表）：波峰高（轻微），波速慢（轻微），波宽宽（剧烈）
+浮脉（表）：波峰高（轻微），脉搏次数少（轻微），波宽宽（剧烈）
 【标准方】薏苡仁汤</t>
         </is>
       </c>
@@ -28479,7 +28479,7 @@
 【病机】风寒湿邪侵袭经络，以风邪偏盛为主。风性善行、走窜不定。
 【症状】肢体关节酸痛，疼痛游走不定，窜走周身。
 【脉象】
-浮脉（表）：波峰高（剧烈），波速慢（轻微），波宽宽（轻微）
+浮脉（表）：波峰高（剧烈），脉搏次数少（轻微），波宽宽（轻微）
 【标准方】防风汤</t>
         </is>
       </c>
@@ -28519,7 +28519,7 @@
 【病机】邪热壅滞于肺，肺失宣降，气机闭塞，热盛气逆。
 【症状】咳嗽气粗、喘促胸闷；痰黄黏稠、不易咳出；发热、口渴咽痛；鼻翼煽动，大便偏干，小便黄。
 【脉象】
-右寸（肺）：波速快
+右寸（肺）：脉搏次数多
 【标准方】麻杏石甘汤</t>
         </is>
       </c>
@@ -28639,7 +28639,7 @@
 【病机】肺阴亏虚，虚火内生，肺失滋润、清肃无权。
 【症状】干咳无痰，或痰少黏稠难咯；咽干口燥、声音嘶哑；潮热盗汗、五心烦热；颧红、形体消瘦。
 【脉象】
-右寸（肺）：波速快，波宽窄
+右寸（肺）：脉搏次数多，波宽窄
 【标准方】沙参麦冬汤</t>
         </is>
       </c>
@@ -28679,7 +28679,7 @@
 【病机】邪热入里，灼津成痰、痰热互结，壅遏肺气，肺失宣降。
 【症状】咳嗽气喘，痰多黄稠、黏稠难咯；胸闷胸痛，甚则鼻翼煽动；发热口渴、烦躁、大便干结、小便黄。
 【脉象】
-右寸（肺）：波速快，波宽宽
+右寸（肺）：脉搏次数多，波宽宽
 【标准方】清气化痰丸</t>
         </is>
       </c>
@@ -28719,8 +28719,8 @@
 【病机】寒邪束表，里有郁热，寒热错杂。
 【症状】怕冷无汗，口干咽痛，浑身酸痛怕冷，同时心烦燥热。
 【脉象】
-浮脉（表）：波速慢
-右寸（肺）：波速快
+浮脉（表）：脉搏次数少
+右寸（肺）：脉搏次数多
 【标准方】大青龙汤</t>
         </is>
       </c>
@@ -28760,8 +28760,8 @@
 【病机】外感风寒，寒邪束表；内有水饮伏肺，表里寒邪相合，寒饮壅遏肺气。
 【症状】恶寒发热，咳嗽气喘；痰多清稀，胸闷胸满，面部浮肿。
 【脉象】
-浮脉（表）：波速慢
-右寸（肺）：波速慢，波宽宽
+浮脉（表）：脉搏次数少
+右寸（肺）：波宽宽
 【标准方】小青龙汤</t>
         </is>
       </c>
@@ -28881,7 +28881,7 @@
 【病机】脾气久虚，脾阳不足、虚寒内生、运化腐熟无权。
 【症状】食少纳呆、脘腹冷痛，喜温喜按；大便清稀溏薄，甚至完谷不化；畏寒肢冷、四肢不温、神疲乏力；口淡不渴、面色㿠白或萎黄；或肢体浮肿、白带清稀量多。
 【脉象】
-右关（脾）：波峰低，波速慢，波宽宽
+右关（脾）：波峰低，脉搏次数少，波宽宽
 【标准方】理中丸</t>
         </is>
       </c>
@@ -28961,7 +28961,7 @@
 【病机】外感风寒之邪束表，内伤饮食湿浊阻滞中焦；表有风寒、里有湿滞。
 【症状】外感风寒：恶寒发热、头痛身重、无汗、鼻塞流清涕；内伤湿滞：胸膈满闷、脘腹胀痛、恶心呕吐、肠鸣泄泻；怕冷发热 + 又吐又泻、身重胸闷。
 【脉象】
-浮脉（表）：波速慢
+浮脉（表）：脉搏次数少
 右关（脾）：波宽宽
 【标准方】藿香正气散</t>
         </is>
@@ -29002,7 +29002,7 @@
 【病机】素体阳虚，阴寒凝滞，寒邪痹阻心脉、胸阳不振，心脉拘急不通而痛。
 【症状】猝然胸痛、痛势剧烈、遇寒加重、得温痛减；胸闷气短、心悸怔忡；畏寒肢冷、面色苍白、唇甲青紫。
 【脉象】
-左寸（心）：波速慢
+左寸（心）：脉搏次数少
 【标准方】当归四逆汤</t>
         </is>
       </c>
@@ -29042,7 +29042,7 @@
 【病机】心火内炽，火热扰心、灼伤脉络、下移小肠。
 【症状】心胸烦热、心悸失眠、烦躁易怒；口舌生疮、舌尖红赤疼痛；口干口苦、面红目赤；小便短赤、灼热涩痛。
 【脉象】
-左寸（心）：波速快
+左寸（心）：脉搏次数多
 【标准方】导赤散</t>
         </is>
       </c>
@@ -29202,7 +29202,7 @@
 【病机】心阴亏虚，心神失养，虚火内扰。
 【症状】心悸怔忡，心慌不安；心烦失眠、多梦易醒；五心烦热、潮热盗汗；口干咽燥、面色颧红。
 【脉象】
-左寸（心）：波线细，波速快，波宽窄
+左寸（心）：波线细，脉搏次数多，波宽窄
 【标准方】天王补心丹</t>
         </is>
       </c>
@@ -29242,7 +29242,7 @@
 【病机】心阳不足，温煦、鼓动无力，虚寒内生。
 【症状】心悸怔忡，心慌不安；胸闷气短、遇寒加重；畏寒怕冷、四肢不温；面色㿠白，精神疲乏，自汗。
 【脉象】
-左寸（心）：波峰低，波速慢
+左寸（心）：波峰低，脉搏次数少
 【标准方】桂枝甘草汤</t>
         </is>
       </c>
@@ -29282,7 +29282,7 @@
 【病机】痰浊郁而化火，痰火互结、上扰心神，神明躁动不宁。
 【症状】心烦失眠、躁扰不宁、狂躁易怒；多梦易惊、甚至胡言乱语、哭笑无常；胸闷痞满、口苦、痰多黄稠。
 【脉象】
-左寸（心）：波速快，波宽宽
+左寸（心）：脉搏次数多，波宽宽
 【标准方】黄连温胆汤</t>
         </is>
       </c>
@@ -29363,7 +29363,7 @@
 【病机】肝郁化火、暴怒伤肝，肝火炽盛、气火上逆，属实热证。
 【症状】头晕胀痛、面红目赤、急躁易怒；口苦口干、耳鸣耳聋、胁肋灼痛；失眠多梦、甚至狂躁；吐血、衄血。
 【脉象】
-左关（肝）：波速快
+左关（肝）：脉搏次数多
 【标准方】龙胆泻肝汤</t>
         </is>
       </c>
@@ -29403,7 +29403,7 @@
 【病机】外感寒邪、凝滞肝经，肝脉拘急、气血阻滞、阳气被遏，属实寒证。
 【症状】少腹冷痛、睾丸坠胀冷痛、疝气痛；巅顶头痛、畏寒喜暖、得温痛减、遇寒加重；四肢厥冷、面色青白。
 【脉象】
-左关（肝）：波速慢
+左关（肝）：脉搏次数少
 【标准方】暖肝煎</t>
         </is>
       </c>
@@ -29563,7 +29563,7 @@
 【病机】情志化火、久病耗伤，肝阴不足、虚火内生、头目筋脉失养。
 【症状】头晕耳鸣、两目干涩、视物昏花；胁肋隐隐灼痛、五心烦热；潮热盗汗、口燥咽干、面部烘热；手足蠕动、筋脉拘急。
 【脉象】
-左关（肝）：波线细，波速快，波宽窄
+左关（肝）：波线细，脉搏次数多，波宽窄
 【标准方】一贯煎</t>
         </is>
       </c>
@@ -29603,7 +29603,7 @@
 【病机】肝肾阴虚，阴不制阳、肝阳升发太过、上扰头目，属本虚标实。
 【症状】眩晕耳鸣、头目胀痛、面红目赤；急躁易怒、失眠多梦、腰膝酸软；头重脚轻、步履不稳。
 【脉象】
-左关（肝）：波峰高，波速快
+左关（肝）：波峰高，脉搏次数多
 【标准方】钩藤散</t>
         </is>
       </c>
@@ -29726,7 +29726,7 @@
 【症状】腰膝酸痛、眩晕耳鸣、健忘；潮热盗汗、五心烦热、口燥咽干；男子遗精早泄，女子经少、闭经或崩漏；形体消瘦、失眠多梦。
 【脉象】
 左尺（肾阴）：波线细，波宽窄
-右尺（肾阳）：波速快
+右尺（肾阳）：脉搏次数多
 【标准方】六味地黄丸</t>
         </is>
       </c>
@@ -29767,7 +29767,7 @@
 【症状】腰膝冷痛、酸软无力；畏寒肢冷，尤以下肢为甚；精神萎靡、面色㿠白或黧黑；小便清长、夜尿多、遗尿；男子阳痿早泄，女子宫寒不孕、带下清稀；大便久泄不止、完谷不化、五更泄泻。
 【脉象】
 左尺（肾阴）：波宽宽
-右尺（肾阳）：波峰低，波速慢
+右尺（肾阳）：波峰低，脉搏次数少
 【标准方】金匮肾气丸</t>
         </is>
       </c>
@@ -29808,7 +29808,7 @@
 【症状】周身浮肿，腰以下肿甚，按之凹陷不起；腰膝酸软冷痛，畏寒肢冷；小便短少，或小便不利；心悸气短、喘咳痰稀如水；面色㿠白或灰黯。
 【脉象】
 左尺（肾阴）：波宽宽
-右尺（肾阳）：波峰低，波速慢
+右尺（肾阳）：波峰低，脉搏次数少
 右关（脾）：波宽宽
 【标准方】真武汤</t>
         </is>
@@ -29974,9 +29974,9 @@
 【病机】肾阴不足，不能上滋心火；心火偏亢，不能下温肾水，水火失济、阴阳失调。多由劳神过度、久病耗阴、情志郁而化火所致，多属阴虚火旺。
 【症状】心火亢于上：心烦失眠、多梦易醒、心悸怔忡、口舌生疮；肾阴亏于下：腰膝酸软、眩晕耳鸣、潮热盗汗、五心烦热；失眠多梦 ， 腰膝酸软 ， 夜寐不安。
 【脉象】
-左寸（心）：波速快
+左寸（心）：脉搏次数多
 左尺（肾阴）：波线细，波宽窄
-右尺（肾阳）：波速快
+右尺（肾阳）：脉搏次数多
 【标准方】黄连阿胶汤</t>
         </is>
       </c>
@@ -30016,10 +30016,10 @@
 【病机】外感温热病邪入里，邪热炽盛、入居气分、里热蒸腾、正邪剧争，属实热证。
 【症状】大热：全身壮热、不恶寒反恶热；大汗：热迫津泄、大汗出；大渴：口大渴、喜冷饮；脉洪大。
 【脉象】
-浮脉（表）：波峰高（轻微），波速快（轻微），波宽窄（轻微）
-左寸（心）：波峰高（轻微），波速快（轻微），波宽窄（轻微）
-右寸（肺）：波峰高（剧烈），波速快（剧烈），波宽窄（剧烈）
-右关（脾）：波峰高（剧烈），波速快（剧烈），波宽窄（剧烈）
+浮脉（表）：波峰高（轻微），脉搏次数多（轻微），波宽窄（轻微）
+左寸（心）：波峰高（轻微），脉搏次数多（轻微），波宽窄（轻微）
+右寸（肺）：波峰高（剧烈），脉搏次数多（剧烈），波宽窄（剧烈）
+右关（脾）：波峰高（剧烈），脉搏次数多（剧烈），波宽窄（剧烈）
 【标准方】白虎汤</t>
         </is>
       </c>

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="600" firstSheet="0" activeTab="9" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" state="visible" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Story'!$A$1:$AA$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'StoryLine'!$A$1:$BI$453</definedName>
   </definedNames>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -178,10 +178,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <name val="BIZ UDGothic"/>
+      <charset val="128"/>
       <family val="3"/>
-      <sz val="9"/>
+      <sz val="6"/>
     </font>
     <font>
       <name val="游ゴシック"/>
@@ -521,7 +521,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="162">
     <dxf>
@@ -2428,8 +2428,8 @@
     <col width="25.5" bestFit="1" customWidth="1" style="23" min="7" max="7"/>
     <col width="31.75" bestFit="1" customWidth="1" style="23" min="8" max="8"/>
     <col width="33.875" bestFit="1" customWidth="1" style="23" min="9" max="9"/>
-    <col width="9.125" customWidth="1" style="23" min="10" max="93"/>
-    <col width="9.125" customWidth="1" style="23" min="94" max="16384"/>
+    <col width="9.125" customWidth="1" style="23" min="10" max="94"/>
+    <col width="9.125" customWidth="1" style="23" min="95" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.4" customHeight="1">
@@ -5631,7 +5631,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F47"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.65"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
     <col width="21.75" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
@@ -6836,8 +6836,8 @@
     <col width="8.375" bestFit="1" customWidth="1" style="46" min="16" max="18"/>
     <col width="10.75" customWidth="1" style="46" min="19" max="19"/>
     <col width="10" bestFit="1" customWidth="1" style="46" min="20" max="20"/>
-    <col width="9" customWidth="1" style="47" min="21" max="43"/>
-    <col width="9" customWidth="1" style="47" min="44" max="16384"/>
+    <col width="9" customWidth="1" style="47" min="21" max="44"/>
+    <col width="9" customWidth="1" style="47" min="45" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customFormat="1" customHeight="1" s="46">
@@ -10072,8 +10072,8 @@
     <col width="48" customWidth="1" style="10" min="9" max="9"/>
     <col width="150.5" customWidth="1" style="64" min="10" max="10"/>
     <col width="8.875" customWidth="1" style="66" min="11" max="11"/>
-    <col width="8.875" customWidth="1" style="36" min="12" max="67"/>
-    <col width="8.875" customWidth="1" style="36" min="68" max="16384"/>
+    <col width="8.875" customWidth="1" style="36" min="12" max="68"/>
+    <col width="8.875" customWidth="1" style="36" min="69" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28035,7 +28035,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G114"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
     <col width="37" customWidth="1" style="3" min="1" max="1"/>
     <col width="19.25" customWidth="1" style="3" min="2" max="2"/>
@@ -28398,7 +28398,7 @@
 【病机】风湿热邪侵袭经络关节，或风寒湿邪郁而化热，气血壅滞、经络痹阻。
 【症状】关节红肿灼热、疼痛剧烈；触之发热、拒按，得冷稍舒；发热、口渴、烦躁；肢体屈伸不利。
 【脉象】
-浮脉（表）：波峰高（轻微），脉搏次数多（剧烈），波宽宽（轻微）
+浮脉（表）：波峰高（轻微），脉搏次数多，波宽宽（轻微）
 【标准方】白虎桂枝汤</t>
         </is>
       </c>
@@ -28639,7 +28639,7 @@
 【病机】肺阴亏虚，虚火内生，肺失滋润、清肃无权。
 【症状】干咳无痰，或痰少黏稠难咯；咽干口燥、声音嘶哑；潮热盗汗、五心烦热；颧红、形体消瘦。
 【脉象】
-右寸（肺）：脉搏次数多，波宽窄
+右寸（肺）：波线细，脉搏次数多，波宽窄
 【标准方】沙参麦冬汤</t>
         </is>
       </c>
@@ -29725,8 +29725,8 @@
 【病机】久病耗伤、房劳过度、过服温燥，肾阴亏虚、虚火内生、失于滋养。
 【症状】腰膝酸痛、眩晕耳鸣、健忘；潮热盗汗、五心烦热、口燥咽干；男子遗精早泄，女子经少、闭经或崩漏；形体消瘦、失眠多梦。
 【脉象】
+右尺（肾阳）：脉搏次数多
 左尺（肾阴）：波线细，波宽窄
-右尺（肾阳）：脉搏次数多
 【标准方】六味地黄丸</t>
         </is>
       </c>
@@ -29766,8 +29766,8 @@
 【病机】年老肾亏、久病伤阳、房劳耗损，肾阳亏虚、命门火衰、温煦气化无权。
 【症状】腰膝冷痛、酸软无力；畏寒肢冷，尤以下肢为甚；精神萎靡、面色㿠白或黧黑；小便清长、夜尿多、遗尿；男子阳痿早泄，女子宫寒不孕、带下清稀；大便久泄不止、完谷不化、五更泄泻。
 【脉象】
+右尺（肾阳）：波峰低，脉搏次数少
 左尺（肾阴）：波宽宽
-右尺（肾阳）：波峰低，脉搏次数少
 【标准方】金匮肾气丸</t>
         </is>
       </c>
@@ -29807,9 +29807,9 @@
 【病机】肾阳虚衰，气化无权，水湿内停，泛溢肌肤。
 【症状】周身浮肿，腰以下肿甚，按之凹陷不起；腰膝酸软冷痛，畏寒肢冷；小便短少，或小便不利；心悸气短、喘咳痰稀如水；面色㿠白或灰黯。
 【脉象】
+右关（脾）：波宽宽
+右尺（肾阳）：波峰低，脉搏次数少
 左尺（肾阴）：波宽宽
-右尺（肾阳）：波峰低，脉搏次数少
-右关（脾）：波宽宽
 【标准方】真武汤</t>
         </is>
       </c>
@@ -29850,8 +29850,8 @@
 【症状】小儿五迟五软：立迟、行迟、语迟、发迟、齿迟；囟门迟闭、智力低下、身材矮小。
 成人脑髓失养：头晕耳鸣、健忘失眠、精神迟钝；早衰特征：发脱齿摇、须发早白；骨骼失养：腰膝酸软、足痿无力生殖亏虚：男子精少不育；女子经闭、不孕。
 【脉象】
+右尺（肾阳）：波峰低
 左尺（肾阴）：波线细
-右尺（肾阳）：波峰低
 【标准方】左归丸</t>
         </is>
       </c>
@@ -29891,8 +29891,8 @@
 【病机】久病劳损、年老体弱、房事不节，肾气亏虚、封藏固摄无权，偏虚证、无明显寒热。
 【症状】腰膝酸软、神疲乏力，耳鸣；小便频数清长、夜尿多、遗尿、小便失禁；男子：滑精、早泄；女子：带下清稀量多、胎动易滑。
 【脉象】
+右尺（肾阳）：波峰低
 左尺（肾阴）：波宽宽
-右尺（肾阳）：波峰低
 【标准方】金锁固精丸</t>
         </is>
       </c>
@@ -29932,9 +29932,9 @@
 【病机】气血下聚冲任以养胎元，母体气血为胎元之本。胎之成，成于肾；胎之养，养于脾。
 【症状】恶心呕吐，食入即吐、厌油腻、头晕倦怠；
 【脉象】
+右关（脾）：波宽宽
+右尺（肾阳）：波峰高
 左尺（肾阴）：波线粗
-右尺（肾阳）：波峰高
-右关（脾）：波宽宽
 【标准方】泰山磐石散</t>
         </is>
       </c>
@@ -30223,7 +30223,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AC50"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
     <col width="19" customWidth="1" style="4" min="1" max="1"/>
     <col width="4.5" customWidth="1" style="32" min="2" max="2"/>
@@ -30248,8 +30248,8 @@
     <col width="5.125" customWidth="1" style="35" min="27" max="27"/>
     <col width="5" customWidth="1" style="35" min="28" max="28"/>
     <col width="5.25" customWidth="1" style="35" min="29" max="29"/>
-    <col width="9" customWidth="1" style="9" min="30" max="141"/>
-    <col width="9" customWidth="1" style="9" min="142" max="16384"/>
+    <col width="9" customWidth="1" style="9" min="30" max="142"/>
+    <col width="9" customWidth="1" style="9" min="143" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -30478,13 +30478,13 @@
         </is>
       </c>
       <c r="B8" s="32" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="D8" s="32" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E8" s="32" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -30494,13 +30494,13 @@
         </is>
       </c>
       <c r="B9" s="32" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="D9" s="32" t="n">
         <v>1.5</v>
       </c>
       <c r="E9" s="32" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -30510,10 +30510,10 @@
         </is>
       </c>
       <c r="B10" s="32" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="D10" s="32" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>1.8</v>
@@ -30529,10 +30529,10 @@
         <v>1.8</v>
       </c>
       <c r="D11" s="32" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E11" s="32" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -30571,6 +30571,9 @@
           <t>肺阴虚</t>
         </is>
       </c>
+      <c r="S15" s="32" t="n">
+        <v>0.5</v>
+      </c>
       <c r="T15" s="32" t="n">
         <v>1.5</v>
       </c>
@@ -30801,7 +30804,7 @@
         </is>
       </c>
       <c r="L34" s="33" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -31026,22 +31029,22 @@
         <v>0.7</v>
       </c>
       <c r="N49" s="34" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="P49" s="34" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="Q49" s="34" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="R49" s="32" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="T49" s="32" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="U49" s="32" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="50">
@@ -31059,7 +31062,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.65"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
     <col width="25.5" customWidth="1" style="3" min="1" max="1"/>
     <col width="15.125" customWidth="1" style="3" min="2" max="2"/>
@@ -33313,7 +33316,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G357"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
     <col width="14.375" customWidth="1" style="4" min="1" max="1"/>
     <col width="11.875" customWidth="1" style="4" min="2" max="2"/>
@@ -45092,7 +45095,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M129"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
     <col width="16.25" customWidth="1" style="7" min="1" max="1"/>
     <col width="11.625" customWidth="1" style="7" min="2" max="2"/>
@@ -53584,7 +53587,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.65"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
     <col width="45.625" customWidth="1" min="1" max="1"/>
     <col width="23.5" customWidth="1" min="2" max="2"/>

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -10544,7 +10544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K454"/>
+  <dimension ref="A1:K456"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="18"/>
   <cols>
     <col width="8.75" customWidth="1" style="10" min="1" max="1"/>
@@ -10680,7 +10680,7 @@
       <c r="I3" s="51" t="inlineStr"/>
       <c r="J3" s="53" t="inlineStr">
         <is>
-          <t>李东璧去各地实地考察，采集样本，参考800多种书籍，花费27年，历经三次改写，至万历六年终于完成著作。全书共52卷，载药1892种，方剂11096首，插图1109幅，约190万字。</t>
+          <t>李东璧去各地实地考察，采集样本，参考800多种书籍，历经三次改写，终于完成著作。全书共52卷，载药1892种，方剂11096首，插图1109幅，约190万字。</t>
         </is>
       </c>
       <c r="K3" s="50" t="inlineStr"/>
@@ -27533,20 +27533,24 @@
       </c>
       <c r="E429" s="53" t="inlineStr">
         <is>
-          <t>李言闻</t>
+          <t>吴芷兰</t>
         </is>
       </c>
       <c r="F429" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G429" s="55" t="inlineStr"/>
       <c r="H429" s="55" t="inlineStr"/>
-      <c r="I429" s="55" t="inlineStr"/>
+      <c r="I429" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/027/027_05.png</t>
+        </is>
+      </c>
       <c r="J429" s="68" t="inlineStr">
         <is>
-          <t>东璧，芷兰，咱们去小摊儿坐会儿吃点元宵。</t>
+          <t>哇，放烟花啦！</t>
         </is>
       </c>
       <c r="K429" s="55" t="inlineStr"/>
@@ -27572,24 +27576,20 @@
       </c>
       <c r="E430" s="53" t="inlineStr">
         <is>
-          <t>李言闻</t>
-        </is>
-      </c>
-      <c r="F430" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F430" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G430" s="55" t="inlineStr"/>
       <c r="H430" s="55" t="inlineStr"/>
-      <c r="I430" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/027/027_05.png</t>
-        </is>
-      </c>
-      <c r="J430" s="55" t="inlineStr">
-        <is>
-          <t>干了一年坐堂医，感觉怎么样，和你之前想的一样吗？</t>
+      <c r="I430" s="55" t="inlineStr"/>
+      <c r="J430" s="68" t="inlineStr">
+        <is>
+          <t>真漂亮啊。</t>
         </is>
       </c>
       <c r="K430" s="55" t="inlineStr"/>
@@ -27615,20 +27615,20 @@
       </c>
       <c r="E431" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F431" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F431" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G431" s="55" t="inlineStr"/>
       <c r="H431" s="55" t="inlineStr"/>
       <c r="I431" s="55" t="inlineStr"/>
-      <c r="J431" s="55" t="inlineStr">
-        <is>
-          <t>我倒是挺喜欢这一行，只是赚不到什么钱，苦了您和芷兰了…</t>
+      <c r="J431" s="68" t="inlineStr">
+        <is>
+          <t>东璧，芷兰，咱们去小摊儿坐会儿吃点元宵。</t>
         </is>
       </c>
       <c r="K431" s="55" t="inlineStr"/>
@@ -27654,20 +27654,24 @@
       </c>
       <c r="E432" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
+          <t>李言闻</t>
         </is>
       </c>
       <c r="F432" s="52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G432" s="55" t="inlineStr"/>
       <c r="H432" s="55" t="inlineStr"/>
-      <c r="I432" s="55" t="inlineStr"/>
+      <c r="I432" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/027/027_06.png</t>
+        </is>
+      </c>
       <c r="J432" s="55" t="inlineStr">
         <is>
-          <t>只要咱们一家人能一起平平安安的过日子，我就知足了，要那么多钱做什么。</t>
+          <t>干了一年坐堂医，感觉怎么样，和你之前想的一样吗？</t>
         </is>
       </c>
       <c r="K432" s="55" t="inlineStr"/>
@@ -27693,12 +27697,12 @@
       </c>
       <c r="E433" s="53" t="inlineStr">
         <is>
-          <t>李言闻</t>
-        </is>
-      </c>
-      <c r="F433" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F433" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G433" s="55" t="inlineStr"/>
@@ -27706,7 +27710,7 @@
       <c r="I433" s="55" t="inlineStr"/>
       <c r="J433" s="55" t="inlineStr">
         <is>
-          <t>是啊，一家人平平安安就好啊。</t>
+          <t>我倒是挺喜欢这一行，只是赚不到什么钱，苦了您和芷兰了…</t>
         </is>
       </c>
       <c r="K433" s="55" t="inlineStr"/>
@@ -27732,12 +27736,12 @@
       </c>
       <c r="E434" s="53" t="inlineStr">
         <is>
-          <t>李言闻</t>
+          <t>吴芷兰</t>
         </is>
       </c>
       <c r="F434" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G434" s="55" t="inlineStr"/>
@@ -27745,24 +27749,24 @@
       <c r="I434" s="55" t="inlineStr"/>
       <c r="J434" s="55" t="inlineStr">
         <is>
-          <t>好了，不早了，咱们该回家了。</t>
+          <t>只要咱们一家人能一起平平安安的过日子，我就知足了，要那么多钱做什么。</t>
         </is>
       </c>
       <c r="K434" s="55" t="inlineStr"/>
     </row>
-    <row r="435" ht="30" customHeight="1">
+    <row r="435">
       <c r="A435" s="50" t="inlineStr">
         <is>
-          <t>028_01</t>
+          <t>027</t>
         </is>
       </c>
       <c r="B435" s="50" t="inlineStr">
         <is>
-          <t>曾题名痰火扰心</t>
+          <t>上元灯节</t>
         </is>
       </c>
       <c r="C435" s="50" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D435" s="50" t="inlineStr">
         <is>
@@ -27771,102 +27775,102 @@
       </c>
       <c r="E435" s="53" t="inlineStr">
         <is>
-          <t>曾和</t>
-        </is>
-      </c>
-      <c r="F435" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G435" s="51" t="inlineStr"/>
-      <c r="H435" s="54" t="inlineStr"/>
-      <c r="I435" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J435" s="53" t="inlineStr">
-        <is>
-          <t>大夫啊，您快给看看吧，这孩子整日目光呆滞，叫他也不应，就在那自言自语，嘴里不知道嘟囔这什么，怪邪乎的…</t>
-        </is>
-      </c>
-      <c r="K435" s="50" t="inlineStr"/>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F435" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G435" s="55" t="inlineStr"/>
+      <c r="H435" s="55" t="inlineStr"/>
+      <c r="I435" s="55" t="inlineStr"/>
+      <c r="J435" s="55" t="inlineStr">
+        <is>
+          <t>是啊，一家人平平安安就好啊。</t>
+        </is>
+      </c>
+      <c r="K435" s="55" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" s="50" t="inlineStr">
         <is>
+          <t>027</t>
+        </is>
+      </c>
+      <c r="B436" s="50" t="inlineStr">
+        <is>
+          <t>上元灯节</t>
+        </is>
+      </c>
+      <c r="C436" s="50" t="n">
+        <v>30</v>
+      </c>
+      <c r="D436" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E436" s="53" t="inlineStr">
+        <is>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F436" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G436" s="55" t="inlineStr"/>
+      <c r="H436" s="55" t="inlineStr"/>
+      <c r="I436" s="55" t="inlineStr"/>
+      <c r="J436" s="55" t="inlineStr">
+        <is>
+          <t>好了，不早了，咱们该回家了。</t>
+        </is>
+      </c>
+      <c r="K436" s="55" t="inlineStr"/>
+    </row>
+    <row r="437" ht="30" customHeight="1">
+      <c r="A437" s="50" t="inlineStr">
+        <is>
           <t>028_01</t>
         </is>
       </c>
-      <c r="B436" s="50" t="inlineStr">
+      <c r="B437" s="50" t="inlineStr">
         <is>
           <t>曾题名痰火扰心</t>
         </is>
       </c>
-      <c r="C436" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="D436" s="50" t="inlineStr">
+      <c r="C437" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D437" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E436" s="53" t="inlineStr">
-        <is>
-          <t>曾题名</t>
-        </is>
-      </c>
-      <c r="F436" s="54" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G436" s="51" t="inlineStr"/>
-      <c r="H436" s="54" t="inlineStr"/>
-      <c r="I436" s="51" t="inlineStr"/>
-      <c r="J436" s="53" t="inlineStr">
-        <is>
-          <t>…</t>
-        </is>
-      </c>
-      <c r="K436" s="50" t="inlineStr"/>
-    </row>
-    <row r="437">
-      <c r="A437" s="50" t="inlineStr">
-        <is>
-          <t>028_01</t>
-        </is>
-      </c>
-      <c r="B437" s="50" t="inlineStr">
-        <is>
-          <t>曾题名痰火扰心</t>
-        </is>
-      </c>
-      <c r="C437" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="D437" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
       <c r="E437" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F437" s="54" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>曾和</t>
+        </is>
+      </c>
+      <c r="F437" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G437" s="51" t="inlineStr"/>
       <c r="H437" s="54" t="inlineStr"/>
-      <c r="I437" s="51" t="inlineStr"/>
+      <c r="I437" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
       <c r="J437" s="53" t="inlineStr">
         <is>
-          <t>别急，坐下来让我看看。</t>
+          <t>大夫啊，您快给看看吧，这孩子整日目光呆滞，叫他也不应，就在那自言自语，嘴里不知道嘟囔这什么，怪邪乎的…</t>
         </is>
       </c>
       <c r="K437" s="50" t="inlineStr"/>
@@ -27883,34 +27887,46 @@
         </is>
       </c>
       <c r="C438" s="50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D438" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E438" s="50" t="inlineStr"/>
-      <c r="F438" s="51" t="inlineStr"/>
+      <c r="E438" s="53" t="inlineStr">
+        <is>
+          <t>曾题名</t>
+        </is>
+      </c>
+      <c r="F438" s="54" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
       <c r="G438" s="51" t="inlineStr"/>
-      <c r="H438" s="51" t="inlineStr"/>
+      <c r="H438" s="54" t="inlineStr"/>
       <c r="I438" s="51" t="inlineStr"/>
-      <c r="J438" s="50" t="inlineStr"/>
+      <c r="J438" s="53" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
       <c r="K438" s="50" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" s="50" t="inlineStr">
         <is>
-          <t>028_02</t>
+          <t>028_01</t>
         </is>
       </c>
       <c r="B439" s="50" t="inlineStr">
         <is>
-          <t>028治疗成功</t>
+          <t>曾题名痰火扰心</t>
         </is>
       </c>
       <c r="C439" s="50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D439" s="50" t="inlineStr">
         <is>
@@ -27922,21 +27938,17 @@
           <t>李东璧</t>
         </is>
       </c>
-      <c r="F439" s="52" t="inlineStr">
+      <c r="F439" s="54" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
       <c r="G439" s="51" t="inlineStr"/>
       <c r="H439" s="54" t="inlineStr"/>
-      <c r="I439" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
+      <c r="I439" s="51" t="inlineStr"/>
       <c r="J439" s="53" t="inlineStr">
         <is>
-          <t>公子所患的是痰迷心窍之症，开副涤痰汤调理一下。</t>
+          <t>别急，坐下来让我看看。</t>
         </is>
       </c>
       <c r="K439" s="50" t="inlineStr"/>
@@ -27944,40 +27956,28 @@
     <row r="440">
       <c r="A440" s="50" t="inlineStr">
         <is>
-          <t>028_02</t>
+          <t>028_01</t>
         </is>
       </c>
       <c r="B440" s="50" t="inlineStr">
         <is>
-          <t>028治疗成功</t>
+          <t>曾题名痰火扰心</t>
         </is>
       </c>
       <c r="C440" s="50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D440" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E440" s="53" t="inlineStr">
-        <is>
-          <t>曾和</t>
-        </is>
-      </c>
-      <c r="F440" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+      <c r="E440" s="50" t="inlineStr"/>
+      <c r="F440" s="51" t="inlineStr"/>
       <c r="G440" s="51" t="inlineStr"/>
-      <c r="H440" s="54" t="inlineStr"/>
+      <c r="H440" s="51" t="inlineStr"/>
       <c r="I440" s="51" t="inlineStr"/>
-      <c r="J440" s="53" t="inlineStr">
-        <is>
-          <t>好好的怎么就得了这怪病呢？</t>
-        </is>
-      </c>
+      <c r="J440" s="50" t="inlineStr"/>
       <c r="K440" s="50" t="inlineStr"/>
     </row>
     <row r="441">
@@ -27992,7 +27992,7 @@
         </is>
       </c>
       <c r="C441" s="50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D441" s="50" t="inlineStr">
         <is>
@@ -28010,11 +28010,15 @@
         </is>
       </c>
       <c r="G441" s="51" t="inlineStr"/>
-      <c r="H441" s="51" t="inlineStr"/>
-      <c r="I441" s="51" t="inlineStr"/>
+      <c r="H441" s="54" t="inlineStr"/>
+      <c r="I441" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
       <c r="J441" s="53" t="inlineStr">
         <is>
-          <t>是不是读书压力太大了呀？</t>
+          <t>公子所患的是痰迷心窍之症，开副涤痰汤调理一下。</t>
         </is>
       </c>
       <c r="K441" s="50" t="inlineStr"/>
@@ -28031,7 +28035,7 @@
         </is>
       </c>
       <c r="C442" s="50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D442" s="50" t="inlineStr">
         <is>
@@ -28040,20 +28044,20 @@
       </c>
       <c r="E442" s="53" t="inlineStr">
         <is>
-          <t>曾题名</t>
+          <t>曾和</t>
         </is>
       </c>
       <c r="F442" s="54" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G442" s="51" t="inlineStr"/>
-      <c r="H442" s="51" t="inlineStr"/>
+      <c r="H442" s="54" t="inlineStr"/>
       <c r="I442" s="51" t="inlineStr"/>
       <c r="J442" s="53" t="inlineStr">
         <is>
-          <t>…</t>
+          <t>好好的怎么就得了这怪病呢？</t>
         </is>
       </c>
       <c r="K442" s="50" t="inlineStr"/>
@@ -28070,7 +28074,7 @@
         </is>
       </c>
       <c r="C443" s="50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D443" s="50" t="inlineStr">
         <is>
@@ -28079,12 +28083,12 @@
       </c>
       <c r="E443" s="53" t="inlineStr">
         <is>
-          <t>曾和</t>
-        </is>
-      </c>
-      <c r="F443" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F443" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G443" s="51" t="inlineStr"/>
@@ -28092,7 +28096,7 @@
       <c r="I443" s="51" t="inlineStr"/>
       <c r="J443" s="53" t="inlineStr">
         <is>
-          <t>他就一门心思读书，其他的什么都不用他管，能有什么压力？</t>
+          <t>是不是读书压力太大了呀？</t>
         </is>
       </c>
       <c r="K443" s="50" t="inlineStr"/>
@@ -28109,7 +28113,7 @@
         </is>
       </c>
       <c r="C444" s="50" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D444" s="50" t="inlineStr">
         <is>
@@ -28118,23 +28122,23 @@
       </c>
       <c r="E444" s="53" t="inlineStr">
         <is>
-          <t>曾和</t>
+          <t>曾题名</t>
         </is>
       </c>
       <c r="F444" s="54" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G444" s="55" t="inlineStr"/>
-      <c r="H444" s="55" t="inlineStr"/>
-      <c r="I444" s="55" t="inlineStr"/>
-      <c r="J444" s="56" t="inlineStr">
-        <is>
-          <t>再说了天下那么多读书人，怎么就他得了这怪病？</t>
-        </is>
-      </c>
-      <c r="K444" s="55" t="inlineStr"/>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G444" s="51" t="inlineStr"/>
+      <c r="H444" s="51" t="inlineStr"/>
+      <c r="I444" s="51" t="inlineStr"/>
+      <c r="J444" s="53" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K444" s="50" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" s="50" t="inlineStr">
@@ -28148,7 +28152,7 @@
         </is>
       </c>
       <c r="C445" s="50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D445" s="50" t="inlineStr">
         <is>
@@ -28157,12 +28161,12 @@
       </c>
       <c r="E445" s="53" t="inlineStr">
         <is>
-          <t>曾题名</t>
+          <t>曾和</t>
         </is>
       </c>
       <c r="F445" s="54" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G445" s="51" t="inlineStr"/>
@@ -28170,10 +28174,10 @@
       <c r="I445" s="51" t="inlineStr"/>
       <c r="J445" s="53" t="inlineStr">
         <is>
-          <t>…</t>
-        </is>
-      </c>
-      <c r="K445" s="55" t="inlineStr"/>
+          <t>他就一门心思读书，其他的什么都不用他管，能有什么压力？</t>
+        </is>
+      </c>
+      <c r="K445" s="50" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" s="50" t="inlineStr">
@@ -28187,7 +28191,7 @@
         </is>
       </c>
       <c r="C446" s="50" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D446" s="50" t="inlineStr">
         <is>
@@ -28196,20 +28200,20 @@
       </c>
       <c r="E446" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F446" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>曾和</t>
+        </is>
+      </c>
+      <c r="F446" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G446" s="55" t="inlineStr"/>
       <c r="H446" s="55" t="inlineStr"/>
       <c r="I446" s="55" t="inlineStr"/>
-      <c r="J446" s="53" t="inlineStr">
-        <is>
-          <t>很多人表面上看着正常，其实都病得不轻呢。</t>
+      <c r="J446" s="56" t="inlineStr">
+        <is>
+          <t>再说了天下那么多读书人，怎么就他得了这怪病？</t>
         </is>
       </c>
       <c r="K446" s="55" t="inlineStr"/>
@@ -28226,7 +28230,7 @@
         </is>
       </c>
       <c r="C447" s="50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D447" s="50" t="inlineStr">
         <is>
@@ -28235,20 +28239,20 @@
       </c>
       <c r="E447" s="53" t="inlineStr">
         <is>
-          <t>曾和</t>
+          <t>曾题名</t>
         </is>
       </c>
       <c r="F447" s="54" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G447" s="55" t="inlineStr"/>
-      <c r="H447" s="55" t="inlineStr"/>
-      <c r="I447" s="55" t="inlineStr"/>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G447" s="51" t="inlineStr"/>
+      <c r="H447" s="51" t="inlineStr"/>
+      <c r="I447" s="51" t="inlineStr"/>
       <c r="J447" s="53" t="inlineStr">
         <is>
-          <t>胡扯，我看你就是没病说成有病，骗病人买药赚钱</t>
+          <t>…</t>
         </is>
       </c>
       <c r="K447" s="55" t="inlineStr"/>
@@ -28265,7 +28269,7 @@
         </is>
       </c>
       <c r="C448" s="50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D448" s="50" t="inlineStr">
         <is>
@@ -28274,12 +28278,12 @@
       </c>
       <c r="E448" s="53" t="inlineStr">
         <is>
-          <t>曾和</t>
-        </is>
-      </c>
-      <c r="F448" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F448" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G448" s="55" t="inlineStr"/>
@@ -28287,7 +28291,7 @@
       <c r="I448" s="55" t="inlineStr"/>
       <c r="J448" s="53" t="inlineStr">
         <is>
-          <t>咱们家可是花了好多钱，把地都卖了供你读书，就只望着你能出人头地，光宗耀祖。可你怎么就这么不争气呢？</t>
+          <t>很多人表面上看着正常，其实都病得不轻呢。</t>
         </is>
       </c>
       <c r="K448" s="55" t="inlineStr"/>
@@ -28304,7 +28308,7 @@
         </is>
       </c>
       <c r="C449" s="50" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D449" s="50" t="inlineStr">
         <is>
@@ -28313,12 +28317,12 @@
       </c>
       <c r="E449" s="53" t="inlineStr">
         <is>
-          <t>曾题名</t>
+          <t>曾和</t>
         </is>
       </c>
       <c r="F449" s="54" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G449" s="55" t="inlineStr"/>
@@ -28326,7 +28330,7 @@
       <c r="I449" s="55" t="inlineStr"/>
       <c r="J449" s="53" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>胡扯，我看你就是没病说成有病，骗病人买药赚钱</t>
         </is>
       </c>
       <c r="K449" s="55" t="inlineStr"/>
@@ -28343,7 +28347,7 @@
         </is>
       </c>
       <c r="C450" s="50" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D450" s="50" t="inlineStr">
         <is>
@@ -28352,20 +28356,20 @@
       </c>
       <c r="E450" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F450" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>曾和</t>
+        </is>
+      </c>
+      <c r="F450" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G450" s="55" t="inlineStr"/>
       <c r="H450" s="55" t="inlineStr"/>
       <c r="I450" s="55" t="inlineStr"/>
-      <c r="J450" s="85" t="inlineStr">
-        <is>
-          <t>这位仁兄，我也是读过书考过科举的，读书人其实也是有很多难处的。</t>
+      <c r="J450" s="53" t="inlineStr">
+        <is>
+          <t>咱们家可是花了好多钱，把地都卖了供你读书，就只望着你能出人头地，光宗耀祖。可你怎么就这么不争气呢？</t>
         </is>
       </c>
       <c r="K450" s="55" t="inlineStr"/>
@@ -28382,7 +28386,7 @@
         </is>
       </c>
       <c r="C451" s="50" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D451" s="50" t="inlineStr">
         <is>
@@ -28391,20 +28395,20 @@
       </c>
       <c r="E451" s="53" t="inlineStr">
         <is>
-          <t>曾和</t>
+          <t>曾题名</t>
         </is>
       </c>
       <c r="F451" s="54" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G451" s="55" t="inlineStr"/>
       <c r="H451" s="55" t="inlineStr"/>
       <c r="I451" s="55" t="inlineStr"/>
-      <c r="J451" s="85" t="inlineStr">
-        <is>
-          <t>难？还能有我赚钱养家糊口难？天底下还能有比我们做父母更难的？</t>
+      <c r="J451" s="53" t="inlineStr">
+        <is>
+          <t>...</t>
         </is>
       </c>
       <c r="K451" s="55" t="inlineStr"/>
@@ -28421,7 +28425,7 @@
         </is>
       </c>
       <c r="C452" s="50" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D452" s="50" t="inlineStr">
         <is>
@@ -28430,12 +28434,12 @@
       </c>
       <c r="E452" s="53" t="inlineStr">
         <is>
-          <t>曾和</t>
-        </is>
-      </c>
-      <c r="F452" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F452" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G452" s="55" t="inlineStr"/>
@@ -28443,7 +28447,7 @@
       <c r="I452" s="55" t="inlineStr"/>
       <c r="J452" s="85" t="inlineStr">
         <is>
-          <t>再过半年可就要考试了，你这次无论如何也要给我好好考。</t>
+          <t>这位仁兄，我也是读过书考过科举的，读书人其实也是有很多难处的。</t>
         </is>
       </c>
       <c r="K452" s="55" t="inlineStr"/>
@@ -28460,7 +28464,7 @@
         </is>
       </c>
       <c r="C453" s="50" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D453" s="50" t="inlineStr">
         <is>
@@ -28469,12 +28473,12 @@
       </c>
       <c r="E453" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F453" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>曾和</t>
+        </is>
+      </c>
+      <c r="F453" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G453" s="55" t="inlineStr"/>
@@ -28482,7 +28486,7 @@
       <c r="I453" s="55" t="inlineStr"/>
       <c r="J453" s="85" t="inlineStr">
         <is>
-          <t>…</t>
+          <t>难？还能有我赚钱养家糊口难？天底下还能有比我们做父母更难的？</t>
         </is>
       </c>
       <c r="K453" s="55" t="inlineStr"/>
@@ -28490,45 +28494,123 @@
     <row r="454">
       <c r="A454" s="50" t="inlineStr">
         <is>
+          <t>028_02</t>
+        </is>
+      </c>
+      <c r="B454" s="50" t="inlineStr">
+        <is>
+          <t>028治疗成功</t>
+        </is>
+      </c>
+      <c r="C454" s="50" t="n">
+        <v>14</v>
+      </c>
+      <c r="D454" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E454" s="53" t="inlineStr">
+        <is>
+          <t>曾和</t>
+        </is>
+      </c>
+      <c r="F454" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G454" s="55" t="inlineStr"/>
+      <c r="H454" s="55" t="inlineStr"/>
+      <c r="I454" s="55" t="inlineStr"/>
+      <c r="J454" s="85" t="inlineStr">
+        <is>
+          <t>再过半年可就要考试了，你这次无论如何也要给我好好考。</t>
+        </is>
+      </c>
+      <c r="K454" s="55" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" s="50" t="inlineStr">
+        <is>
+          <t>028_02</t>
+        </is>
+      </c>
+      <c r="B455" s="50" t="inlineStr">
+        <is>
+          <t>028治疗成功</t>
+        </is>
+      </c>
+      <c r="C455" s="50" t="n">
+        <v>15</v>
+      </c>
+      <c r="D455" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E455" s="53" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F455" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G455" s="55" t="inlineStr"/>
+      <c r="H455" s="55" t="inlineStr"/>
+      <c r="I455" s="55" t="inlineStr"/>
+      <c r="J455" s="85" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K455" s="55" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" s="50" t="inlineStr">
+        <is>
           <t>028_03</t>
         </is>
       </c>
-      <c r="B454" s="50" t="inlineStr">
+      <c r="B456" s="50" t="inlineStr">
         <is>
           <t>028治疗失败</t>
         </is>
       </c>
-      <c r="C454" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D454" s="50" t="inlineStr">
+      <c r="C456" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D456" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E454" s="53" t="inlineStr">
+      <c r="E456" s="53" t="inlineStr">
         <is>
           <t>李东璧</t>
         </is>
       </c>
-      <c r="F454" s="52" t="inlineStr">
+      <c r="F456" s="52" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="G454" s="51" t="inlineStr"/>
-      <c r="H454" s="54" t="inlineStr"/>
-      <c r="I454" s="51" t="inlineStr">
+      <c r="G456" s="51" t="inlineStr"/>
+      <c r="H456" s="54" t="inlineStr"/>
+      <c r="I456" s="51" t="inlineStr">
         <is>
           <t>current_scene</t>
         </is>
       </c>
-      <c r="J454" s="53" t="inlineStr">
+      <c r="J456" s="53" t="inlineStr">
         <is>
           <t>不对，我需要好好想想这是什么病，该开什么方。</t>
         </is>
       </c>
-      <c r="K454" s="50" t="inlineStr"/>
+      <c r="K456" s="50" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:BI453"/>
